--- a/PPREstimation/output/top10/52_1_Sea_of_Okhotsk_NE_(1980).xlsx
+++ b/PPREstimation/output/top10/52_1_Sea_of_Okhotsk_NE_(1980).xlsx
@@ -701,7 +701,11 @@
           <t>DET</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr"/>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Detritus; nonliving compartment, not a taxon.</t>
+        </is>
+      </c>
       <c r="F3" s="2" t="n">
         <v>1</v>
       </c>
@@ -785,7 +789,11 @@
           <t>PP</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr"/>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Phytoplankton; pelagic primary producers, species membership not documented.</t>
+        </is>
+      </c>
       <c r="F4" s="2" t="n">
         <v>1</v>
       </c>
@@ -869,7 +877,11 @@
           <t>PP</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr"/>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Phytobenthos; benthic primary producers, species membership not documented.</t>
+        </is>
+      </c>
       <c r="F5" s="2" t="n">
         <v>1</v>
       </c>
@@ -953,7 +965,11 @@
           <t>Regular</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr"/>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Herbivorous zooplankton; species membership not documented.</t>
+        </is>
+      </c>
       <c r="F6" s="2" t="n">
         <v>2</v>
       </c>
@@ -1037,7 +1053,11 @@
           <t>Regular</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr"/>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Predatory zooplankton; species membership not documented.</t>
+        </is>
+      </c>
       <c r="F7" s="2" t="n">
         <v>3.207729468599033</v>
       </c>
@@ -1121,7 +1141,11 @@
           <t>Regular</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr"/>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>2nd level benthos; Table 1 trophic-guild label, species membership not documented; Table 3 diet draws from phytoplankton, phytobenthos and detritus.</t>
+        </is>
+      </c>
       <c r="F8" s="2" t="n">
         <v>2</v>
       </c>
@@ -1205,7 +1229,11 @@
           <t>Regular</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr"/>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Carnivorous invertebrates; Table 1 feeding-guild label, species membership not documented; Table 3 diet is second-level benthos.</t>
+        </is>
+      </c>
       <c r="F9" s="2" t="n">
         <v>3</v>
       </c>
@@ -1289,7 +1317,11 @@
           <t>Regular</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr"/>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Jellyfish; Table 1 pool label, no species list.</t>
+        </is>
+      </c>
       <c r="F10" s="2" t="n">
         <v>3.328540248132356</v>
       </c>
@@ -1373,7 +1405,11 @@
           <t>Regular</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr"/>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Squids; Table 1 taxonomic pool label, no species list.</t>
+        </is>
+      </c>
       <c r="F11" s="2" t="n">
         <v>4.187409706042596</v>
       </c>
@@ -1457,7 +1493,11 @@
           <t>Regular</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr"/>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Crabs and shrimps; Table 1 taxonomic pool label, no species list.</t>
+        </is>
+      </c>
       <c r="F12" s="2" t="n">
         <v>3.035190378918355</v>
       </c>
@@ -1541,7 +1581,11 @@
           <t>Regular</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr"/>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Other mesopelagic fishes, excluding the separately named Myctophidae and Bathylagidae; species list not documented.</t>
+        </is>
+      </c>
       <c r="F13" s="2" t="n">
         <v>4.092995169082125</v>
       </c>
@@ -1625,7 +1669,11 @@
           <t>Regular</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr"/>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Bathylagidae; Table 1 family label, no species list.</t>
+        </is>
+      </c>
       <c r="F14" s="2" t="n">
         <v>3.756119284678897</v>
       </c>
@@ -1709,7 +1757,11 @@
           <t>Regular</t>
         </is>
       </c>
-      <c r="E15" t="inlineStr"/>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Myctophidae; Table 1 family label, no species list.</t>
+        </is>
+      </c>
       <c r="F15" s="2" t="n">
         <v>3.204574879227053</v>
       </c>
@@ -1793,7 +1845,11 @@
           <t>Regular</t>
         </is>
       </c>
-      <c r="E16" t="inlineStr"/>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Ammodytidae; Table 1 family label, no species list.</t>
+        </is>
+      </c>
       <c r="F16" s="2" t="n">
         <v>3.003038647342995</v>
       </c>
@@ -1877,7 +1933,11 @@
           <t>Regular</t>
         </is>
       </c>
-      <c r="E17" t="inlineStr"/>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Other bottom fishes; residual bottom-fish pool, species membership not documented in the available chapter.</t>
+        </is>
+      </c>
       <c r="F17" s="2" t="n">
         <v>3.856616903690124</v>
       </c>
@@ -1961,7 +2021,11 @@
           <t>Regular</t>
         </is>
       </c>
-      <c r="E18" t="inlineStr"/>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Cottidae; Table 1 family label, no species list.</t>
+        </is>
+      </c>
       <c r="F18" s="2" t="n">
         <v>4.267368892965685</v>
       </c>
@@ -2045,7 +2109,11 @@
           <t>Regular</t>
         </is>
       </c>
-      <c r="E19" t="inlineStr"/>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Pleuronectidae; Table 1 family label, no species list.</t>
+        </is>
+      </c>
       <c r="F19" s="2" t="n">
         <v>3.394774023413718</v>
       </c>
@@ -2129,7 +2197,11 @@
           <t>Regular</t>
         </is>
       </c>
-      <c r="E20" t="inlineStr"/>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Gadidae other than pollock (pollock has two separate life-stage groups); Table 1 taxonomic label.</t>
+        </is>
+      </c>
       <c r="F20" s="2" t="n">
         <v>3.916894441410394</v>
       </c>
@@ -2213,7 +2285,11 @@
           <t>Regular</t>
         </is>
       </c>
-      <c r="E21" t="inlineStr"/>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Pacific Sardine; binomial and regional synonym treatment not documented in the available chapter.</t>
+        </is>
+      </c>
       <c r="F21" s="2" t="n">
         <v>2.157531400966184</v>
       </c>
@@ -2297,7 +2373,11 @@
           <t>Regular</t>
         </is>
       </c>
-      <c r="E22" t="inlineStr"/>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Capelin; named stock in Table 1. Scientific-name crosswalk Mallotus villosus is a taxonomic interpretation.</t>
+        </is>
+      </c>
       <c r="F22" s="2" t="n">
         <v>3.502415458937198</v>
       </c>
@@ -2381,7 +2461,11 @@
           <t>Regular</t>
         </is>
       </c>
-      <c r="E23" t="inlineStr"/>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Salmon; species membership not documented in the available chapter.</t>
+        </is>
+      </c>
       <c r="F23" s="2" t="n">
         <v>3.877820521458073</v>
       </c>
@@ -2465,7 +2549,11 @@
           <t>Regular</t>
         </is>
       </c>
-      <c r="E24" t="inlineStr"/>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Pacific herring; named stock in Table 1. Scientific-name crosswalk Clupea pallasii is a taxonomic interpretation.</t>
+        </is>
+      </c>
       <c r="F24" s="2" t="n">
         <v>3.953399257747084</v>
       </c>
@@ -2549,7 +2637,11 @@
           <t>Regular</t>
         </is>
       </c>
-      <c r="E25" t="inlineStr"/>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Juvenile walleye pollock; age/length boundary not documented in the available chapter.</t>
+        </is>
+      </c>
       <c r="F25" s="2" t="n">
         <v>3.753316151048269</v>
       </c>
@@ -2633,7 +2725,11 @@
           <t>Regular</t>
         </is>
       </c>
-      <c r="E26" t="inlineStr"/>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Walleye pollock, adult/nonjuvenile compartment; Table 1 separates Juv. pollock. Scientific-name crosswalk Gadus chalcogrammus is a taxonomic interpretation.</t>
+        </is>
+      </c>
       <c r="F26" s="2" t="n">
         <v>3.74445475879728</v>
       </c>
@@ -2717,7 +2813,11 @@
           <t>Regular</t>
         </is>
       </c>
-      <c r="E27" t="inlineStr"/>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>Seabirds; species membership not documented in the available chapter.</t>
+        </is>
+      </c>
       <c r="F27" s="2" t="n">
         <v>4.688743980695794</v>
       </c>
@@ -2801,7 +2901,11 @@
           <t>Regular</t>
         </is>
       </c>
-      <c r="E28" t="inlineStr"/>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>Pinnipeds; species membership not documented in the available chapter.</t>
+        </is>
+      </c>
       <c r="F28" s="2" t="n">
         <v>4.960093888150276</v>
       </c>
@@ -2885,7 +2989,11 @@
           <t>Regular</t>
         </is>
       </c>
-      <c r="E29" t="inlineStr"/>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>Sperm whales; the common-name stock in Table 1, no binomial listed.</t>
+        </is>
+      </c>
       <c r="F29" s="2" t="n">
         <v>5.095145064278068</v>
       </c>
@@ -2969,7 +3077,11 @@
           <t>Regular</t>
         </is>
       </c>
-      <c r="E30" t="inlineStr"/>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>Toothed whales other than the separate sperm-whale compartment; species membership not documented in the available chapter.</t>
+        </is>
+      </c>
       <c r="F30" s="2" t="n">
         <v>4.555881045383044</v>
       </c>
@@ -3053,7 +3165,11 @@
           <t>Regular</t>
         </is>
       </c>
-      <c r="E31" t="inlineStr"/>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>Baleen whales (Mysticeti); Table 1 supplies the group label, not a species list.</t>
+        </is>
+      </c>
       <c r="F31" s="2" t="n">
         <v>3.920339884921915</v>
       </c>
@@ -3576,10 +3692,10 @@
         <v>1.57110834371108</v>
       </c>
       <c r="U6" s="2" t="n">
-        <v>1.933548290327782</v>
+        <v>1.976455960273223</v>
       </c>
       <c r="V6" s="2" t="n">
-        <v>2.255931176841743</v>
+        <v>2.308357824368465</v>
       </c>
     </row>
     <row r="7">
@@ -3640,10 +3756,10 @@
         <v>10.2804066263069</v>
       </c>
       <c r="U7" s="2" t="n">
-        <v>29.81677210884715</v>
+        <v>25.22697108590053</v>
       </c>
       <c r="V7" s="2" t="n">
-        <v>30.45608045009691</v>
+        <v>30.57866372023318</v>
       </c>
     </row>
     <row r="8">
@@ -3704,10 +3820,10 @@
         <v>0.52578947368421</v>
       </c>
       <c r="U8" s="2" t="n">
-        <v>0.6678366192800906</v>
+        <v>0.6687581615728373</v>
       </c>
       <c r="V8" s="2" t="n">
-        <v>1.279315089196931</v>
+        <v>1.266223979894226</v>
       </c>
     </row>
     <row r="9">
@@ -3768,10 +3884,10 @@
         <v>2.83331082423039</v>
       </c>
       <c r="U9" s="2" t="n">
-        <v>4.595370278410042</v>
+        <v>4.634726872264785</v>
       </c>
       <c r="V9" s="2" t="n">
-        <v>10.79309877355778</v>
+        <v>11.09067603768777</v>
       </c>
     </row>
     <row r="10">
@@ -3832,10 +3948,10 @@
         <v>10.35422279740442</v>
       </c>
       <c r="U10" s="2" t="n">
-        <v>40.24919132757497</v>
+        <v>34.86460471498391</v>
       </c>
       <c r="V10" s="2" t="n">
-        <v>7151.146927648732</v>
+        <v>6957.067696845485</v>
       </c>
     </row>
     <row r="11">
@@ -3896,10 +4012,10 @@
         <v>16.65994894282628</v>
       </c>
       <c r="U11" s="2" t="n">
-        <v>62.25996360979219</v>
+        <v>52.97004466733012</v>
       </c>
       <c r="V11" s="2" t="n">
-        <v>131.1665566122365</v>
+        <v>139.2881081991169</v>
       </c>
     </row>
     <row r="12">
@@ -3960,10 +4076,10 @@
         <v>14.87766483205663</v>
       </c>
       <c r="U12" s="2" t="n">
-        <v>48.33257475069331</v>
+        <v>44.22194306053004</v>
       </c>
       <c r="V12" s="2" t="n">
-        <v>77.67171584789311</v>
+        <v>84.73603667840504</v>
       </c>
     </row>
     <row r="13">
@@ -4024,10 +4140,10 @@
         <v>64.15053955979791</v>
       </c>
       <c r="U13" s="2" t="n">
-        <v>228.5200672141292</v>
+        <v>197.5644862262235</v>
       </c>
       <c r="V13" s="2" t="n">
-        <v>231.352947483625</v>
+        <v>241.3358580441285</v>
       </c>
     </row>
     <row r="14">
@@ -4088,10 +4204,10 @@
         <v>33.67490609701579</v>
       </c>
       <c r="U14" s="2" t="n">
-        <v>116.34362576912</v>
+        <v>100.733153871753</v>
       </c>
       <c r="V14" s="2" t="n">
-        <v>912.0015912456159</v>
+        <v>862.9555412761928</v>
       </c>
     </row>
     <row r="15">
@@ -4152,10 +4268,10 @@
         <v>10.6632119618614</v>
       </c>
       <c r="U15" s="2" t="n">
-        <v>28.7711256271498</v>
+        <v>25.69708011456198</v>
       </c>
       <c r="V15" s="2" t="n">
-        <v>61.62672420412056</v>
+        <v>61.00638723800488</v>
       </c>
     </row>
     <row r="16">
@@ -4216,10 +4332,10 @@
         <v>4.60014674738518</v>
       </c>
       <c r="U16" s="2" t="n">
-        <v>8.530071182256405</v>
+        <v>8.256892257374963</v>
       </c>
       <c r="V16" s="2" t="n">
-        <v>29.85879134963909</v>
+        <v>30.16948865601263</v>
       </c>
     </row>
     <row r="17">
@@ -4280,10 +4396,10 @@
         <v>186.5812184500154</v>
       </c>
       <c r="U17" s="2" t="n">
-        <v>1456.107562276347</v>
+        <v>1168.976189206878</v>
       </c>
       <c r="V17" s="2" t="n">
-        <v>2509.280632311686</v>
+        <v>3060.457117583493</v>
       </c>
     </row>
     <row r="18">
@@ -4344,10 +4460,10 @@
         <v>853.0630454865741</v>
       </c>
       <c r="U18" s="2" t="n">
-        <v>21901.51809239904</v>
+        <v>18826.9724226668</v>
       </c>
       <c r="V18" s="2" t="n">
-        <v>182281.0838601563</v>
+        <v>534048.733202767</v>
       </c>
     </row>
     <row r="19">
@@ -4408,10 +4524,10 @@
         <v>72.46490217444796</v>
       </c>
       <c r="U19" s="2" t="n">
-        <v>663.3075554650212</v>
+        <v>528.9993658267483</v>
       </c>
       <c r="V19" s="2" t="n">
-        <v>1168.11314957985</v>
+        <v>1351.256347786268</v>
       </c>
     </row>
     <row r="20">
@@ -4472,10 +4588,10 @@
         <v>749.7648874974424</v>
       </c>
       <c r="U20" s="2" t="n">
-        <v>12987.69536066548</v>
+        <v>11452.21228823698</v>
       </c>
       <c r="V20" s="2" t="n">
-        <v>268180.3665437567</v>
+        <v>802390.1492857393</v>
       </c>
     </row>
     <row r="21">
@@ -4536,10 +4652,10 @@
         <v>7.61123479889308</v>
       </c>
       <c r="U21" s="2" t="n">
-        <v>12.63490502974413</v>
+        <v>11.93647396706558</v>
       </c>
       <c r="V21" s="2" t="n">
-        <v>15.87478402043228</v>
+        <v>16.2610545606418</v>
       </c>
     </row>
     <row r="22">
@@ -4600,10 +4716,10 @@
         <v>37.1421762313681</v>
       </c>
       <c r="U22" s="2" t="n">
-        <v>123.6724109937916</v>
+        <v>105.7724068270841</v>
       </c>
       <c r="V22" s="2" t="n">
-        <v>152.755274624661</v>
+        <v>158.3505104971605</v>
       </c>
     </row>
     <row r="23">
@@ -4664,10 +4780,10 @@
         <v>11.01889812948852</v>
       </c>
       <c r="U23" s="2" t="n">
-        <v>39.08708938100007</v>
+        <v>35.43906310311317</v>
       </c>
       <c r="V23" s="2" t="n">
-        <v>391.301319609375</v>
+        <v>371.5681739455553</v>
       </c>
     </row>
     <row r="24">
@@ -4728,10 +4844,10 @@
         <v>82.919653175905</v>
       </c>
       <c r="U24" s="2" t="n">
-        <v>291.4928456998692</v>
+        <v>251.2924473650104</v>
       </c>
       <c r="V24" s="2" t="n">
-        <v>361.2452629544228</v>
+        <v>382.4625627660487</v>
       </c>
     </row>
     <row r="25">
@@ -4792,10 +4908,10 @@
         <v>193.1895380685191</v>
       </c>
       <c r="U25" s="2" t="n">
-        <v>746.9772810092462</v>
+        <v>653.7568966921568</v>
       </c>
       <c r="V25" s="2" t="n">
-        <v>1428.517865667728</v>
+        <v>1380.632097213146</v>
       </c>
     </row>
     <row r="26">
@@ -4856,10 +4972,10 @@
         <v>160.0875340948016</v>
       </c>
       <c r="U26" s="2" t="n">
-        <v>641.3020859498071</v>
+        <v>555.7535688545403</v>
       </c>
       <c r="V26" s="2" t="n">
-        <v>1250.725035231723</v>
+        <v>1186.451320717368</v>
       </c>
     </row>
     <row r="27">
@@ -4918,7 +5034,7 @@
         <v>28370.40164531038</v>
       </c>
       <c r="U27" s="2" t="n">
-        <v>137834.6678091644</v>
+        <v>119795.9986011631</v>
       </c>
       <c r="V27" s="2" t="n">
         <v>0</v>
@@ -4982,10 +5098,10 @@
         <v>17172.16854500374</v>
       </c>
       <c r="U28" s="2" t="n">
-        <v>120421.094861721</v>
+        <v>104705.1401437606</v>
       </c>
       <c r="V28" s="2" t="n">
-        <v>2268636.255252894</v>
+        <v>6283035.907771785</v>
       </c>
     </row>
     <row r="29">
@@ -5044,7 +5160,7 @@
         <v>5412.614990574212</v>
       </c>
       <c r="U29" s="2" t="n">
-        <v>33948.58077083328</v>
+        <v>28246.56755723941</v>
       </c>
       <c r="V29" s="2" t="n">
         <v>0</v>
@@ -5108,10 +5224,10 @@
         <v>118144.287920584</v>
       </c>
       <c r="U30" s="2" t="n">
-        <v>1257895.064038356</v>
+        <v>1069075.741170226</v>
       </c>
       <c r="V30" s="2" t="n">
-        <v>206372811.5273508</v>
+        <v>693202949.0927888</v>
       </c>
     </row>
     <row r="31">
@@ -5172,10 +5288,10 @@
         <v>10707.24960245817</v>
       </c>
       <c r="U31" s="2" t="n">
-        <v>51371.24286009844</v>
+        <v>44276.76767744365</v>
       </c>
       <c r="V31" s="2" t="n">
-        <v>246957.8827580145</v>
+        <v>242675.1433360545</v>
       </c>
     </row>
   </sheetData>
@@ -5456,10 +5572,10 @@
         <v>1.215966569657497</v>
       </c>
       <c r="U3" s="2" t="n">
-        <v>1.479754746589097</v>
+        <v>1.55744703420373</v>
       </c>
       <c r="V3" s="2" t="n">
-        <v>0.9524282247900254</v>
+        <v>0.9515593841782986</v>
       </c>
     </row>
     <row r="4">
@@ -5666,10 +5782,10 @@
         <v>3.481523566973713</v>
       </c>
       <c r="U6" s="2" t="n">
-        <v>4.8059587400622</v>
+        <v>5.128465854802356</v>
       </c>
       <c r="V6" s="2" t="n">
-        <v>4.40689454275917</v>
+        <v>4.505329171349933</v>
       </c>
     </row>
     <row r="7">
@@ -5736,10 +5852,10 @@
         <v>22.7810374063815</v>
       </c>
       <c r="U7" s="2" t="n">
-        <v>81.43857103579776</v>
+        <v>69.8307226009985</v>
       </c>
       <c r="V7" s="2" t="n">
-        <v>59.6082356678519</v>
+        <v>59.77915649033152</v>
       </c>
     </row>
     <row r="8">
@@ -5806,10 +5922,10 @@
         <v>2.017588459932436</v>
       </c>
       <c r="U8" s="2" t="n">
-        <v>2.983492934349642</v>
+        <v>3.13336965565452</v>
       </c>
       <c r="V8" s="2" t="n">
-        <v>4.12098512225864</v>
+        <v>4.076903184343629</v>
       </c>
     </row>
     <row r="9">
@@ -5876,10 +5992,10 @@
         <v>10.87213705956044</v>
       </c>
       <c r="U9" s="2" t="n">
-        <v>20.37665927427547</v>
+        <v>21.3717736299582</v>
       </c>
       <c r="V9" s="2" t="n">
-        <v>34.77571014872512</v>
+        <v>35.71211791968918</v>
       </c>
     </row>
     <row r="10">
@@ -5946,10 +6062,10 @@
         <v>25.48900096933077</v>
       </c>
       <c r="U10" s="2" t="n">
-        <v>115.4182934698164</v>
+        <v>106.2196904182567</v>
       </c>
       <c r="V10" s="2" t="n">
-        <v>15241.14851623251</v>
+        <v>14877.93741284232</v>
       </c>
     </row>
     <row r="11">
@@ -6016,10 +6132,10 @@
         <v>37.01493907846017</v>
       </c>
       <c r="U11" s="2" t="n">
-        <v>170.6887237543336</v>
+        <v>147.5812828659979</v>
       </c>
       <c r="V11" s="2" t="n">
-        <v>257.6673176573593</v>
+        <v>273.2189846219271</v>
       </c>
     </row>
     <row r="12">
@@ -6086,10 +6202,10 @@
         <v>44.38971537530528</v>
       </c>
       <c r="U12" s="2" t="n">
-        <v>155.2398939433816</v>
+        <v>155.5269499733022</v>
       </c>
       <c r="V12" s="2" t="n">
-        <v>187.5776355700277</v>
+        <v>203.4330067474349</v>
       </c>
     </row>
     <row r="13">
@@ -6156,10 +6272,10 @@
         <v>142.1843919903361</v>
       </c>
       <c r="U13" s="2" t="n">
-        <v>619.2551609800333</v>
+        <v>550.6230027330051</v>
       </c>
       <c r="V13" s="2" t="n">
-        <v>453.0361372714805</v>
+        <v>471.8097034434562</v>
       </c>
     </row>
     <row r="14">
@@ -6226,10 +6342,10 @@
         <v>75.9453993065396</v>
       </c>
       <c r="U14" s="2" t="n">
-        <v>320.822432898238</v>
+        <v>288.5903086732923</v>
       </c>
       <c r="V14" s="2" t="n">
-        <v>1821.949146666326</v>
+        <v>1722.34384103534</v>
       </c>
     </row>
     <row r="15">
@@ -6296,10 +6412,10 @@
         <v>23.98142182176431</v>
       </c>
       <c r="U15" s="2" t="n">
-        <v>77.57888239456308</v>
+        <v>68.98158964326262</v>
       </c>
       <c r="V15" s="2" t="n">
-        <v>123.2087982286978</v>
+        <v>121.8463895038143</v>
       </c>
     </row>
     <row r="16">
@@ -6366,10 +6482,10 @@
         <v>17.40210571612738</v>
       </c>
       <c r="U16" s="2" t="n">
-        <v>36.10829061840167</v>
+        <v>36.80762559128662</v>
       </c>
       <c r="V16" s="2" t="n">
-        <v>93.50725180020996</v>
+        <v>94.42462805535909</v>
       </c>
     </row>
     <row r="17">
@@ -6436,10 +6552,10 @@
         <v>441.4514780752895</v>
       </c>
       <c r="U17" s="2" t="n">
-        <v>4543.691069600135</v>
+        <v>3363.787374222307</v>
       </c>
       <c r="V17" s="2" t="n">
-        <v>5107.845289991419</v>
+        <v>6233.035289922082</v>
       </c>
     </row>
     <row r="18">
@@ -6506,10 +6622,10 @@
         <v>2098.815049380803</v>
       </c>
       <c r="U18" s="2" t="n">
-        <v>77538.51278903786</v>
+        <v>125580.9580385296</v>
       </c>
       <c r="V18" s="2" t="n">
-        <v>376102.081527669</v>
+        <v>1095224.597367184</v>
       </c>
     </row>
     <row r="19">
@@ -6576,10 +6692,10 @@
         <v>181.1546416749435</v>
       </c>
       <c r="U19" s="2" t="n">
-        <v>2141.070009355116</v>
+        <v>1563.239343021115</v>
       </c>
       <c r="V19" s="2" t="n">
-        <v>2413.536958955666</v>
+        <v>2786.139764177064</v>
       </c>
     </row>
     <row r="20">
@@ -6646,10 +6762,10 @@
         <v>1835.974420509146</v>
       </c>
       <c r="U20" s="2" t="n">
-        <v>45014.36440658045</v>
+        <v>68000.60919240557</v>
       </c>
       <c r="V20" s="2" t="n">
-        <v>553523.0843808699</v>
+        <v>1645094.341484428</v>
       </c>
     </row>
     <row r="21">
@@ -6716,10 +6832,10 @@
         <v>10.35309527955403</v>
       </c>
       <c r="U21" s="2" t="n">
-        <v>22.31424320996268</v>
+        <v>20.67031609222641</v>
       </c>
       <c r="V21" s="2" t="n">
-        <v>23.08419125913939</v>
+        <v>23.7201163809729</v>
       </c>
     </row>
     <row r="22">
@@ -6786,10 +6902,10 @@
         <v>82.5145022198011</v>
       </c>
       <c r="U22" s="2" t="n">
-        <v>337.6323632192312</v>
+        <v>299.6056369087224</v>
       </c>
       <c r="V22" s="2" t="n">
-        <v>299.6173327395348</v>
+        <v>310.1782655945706</v>
       </c>
     </row>
     <row r="23">
@@ -6856,10 +6972,10 @@
         <v>24.5480268157923</v>
       </c>
       <c r="U23" s="2" t="n">
-        <v>105.8865341817734</v>
+        <v>98.75863916971537</v>
       </c>
       <c r="V23" s="2" t="n">
-        <v>808.0683034516113</v>
+        <v>768.3150282244065</v>
       </c>
     </row>
     <row r="24">
@@ -6926,10 +7042,10 @@
         <v>184.0673282958193</v>
       </c>
       <c r="U24" s="2" t="n">
-        <v>795.9394278252513</v>
+        <v>701.5793292129669</v>
       </c>
       <c r="V24" s="2" t="n">
-        <v>707.689575465899</v>
+        <v>748.5026573846656</v>
       </c>
     </row>
     <row r="25">
@@ -6996,10 +7112,10 @@
         <v>438.8976480164774</v>
       </c>
       <c r="U25" s="2" t="n">
-        <v>2045.106697564957</v>
+        <v>1890.2154688351</v>
       </c>
       <c r="V25" s="2" t="n">
-        <v>2865.160909975357</v>
+        <v>2766.021116765205</v>
       </c>
     </row>
     <row r="26">
@@ -7066,10 +7182,10 @@
         <v>356.6715646359351</v>
       </c>
       <c r="U26" s="2" t="n">
-        <v>1753.2113843777</v>
+        <v>1571.516221606758</v>
       </c>
       <c r="V26" s="2" t="n">
-        <v>2483.004557003551</v>
+        <v>2351.352010120519</v>
       </c>
     </row>
     <row r="27">
@@ -7134,7 +7250,7 @@
         <v>64351.12625726748</v>
       </c>
       <c r="U27" s="2" t="n">
-        <v>380326.7529397003</v>
+        <v>337644.5780228017</v>
       </c>
       <c r="V27" s="2" t="n">
         <v>0</v>
@@ -7204,10 +7320,10 @@
         <v>38693.42214073123</v>
       </c>
       <c r="U28" s="2" t="n">
-        <v>372197.7840953156</v>
+        <v>444402.7360572153</v>
       </c>
       <c r="V28" s="2" t="n">
-        <v>4663973.032452663</v>
+        <v>12867258.24483938</v>
       </c>
     </row>
     <row r="29">
@@ -7272,7 +7388,7 @@
         <v>12359.60479087096</v>
       </c>
       <c r="U29" s="2" t="n">
-        <v>98244.16132433986</v>
+        <v>80536.99363237218</v>
       </c>
       <c r="V29" s="2" t="n">
         <v>0</v>
@@ -7342,10 +7458,10 @@
         <v>271730.3462542624</v>
       </c>
       <c r="U30" s="2" t="n">
-        <v>3785171.073549521</v>
+        <v>3850028.862905373</v>
       </c>
       <c r="V30" s="2" t="n">
-        <v>425797580.7539435</v>
+        <v>1414639309.654173</v>
       </c>
     </row>
     <row r="31">
@@ -7412,10 +7528,10 @@
         <v>24175.56556988574</v>
       </c>
       <c r="U31" s="2" t="n">
-        <v>140024.3572726357</v>
+        <v>128841.0239714557</v>
       </c>
       <c r="V31" s="2" t="n">
-        <v>493327.6906105255</v>
+        <v>484185.117512574</v>
       </c>
     </row>
   </sheetData>
@@ -7696,10 +7812,10 @@
         <v>1.215966569657497</v>
       </c>
       <c r="U3" s="2" t="n">
-        <v>1.479754746589097</v>
+        <v>1.55744703420373</v>
       </c>
       <c r="V3" s="2" t="n">
-        <v>0.9524282247900254</v>
+        <v>0.9515593841782986</v>
       </c>
     </row>
     <row r="4">
@@ -7906,10 +8022,10 @@
         <v>3.481523566973713</v>
       </c>
       <c r="U6" s="2" t="n">
-        <v>4.8059587400622</v>
+        <v>5.128465854802356</v>
       </c>
       <c r="V6" s="2" t="n">
-        <v>4.40689454275917</v>
+        <v>4.505329171349933</v>
       </c>
     </row>
     <row r="7">
@@ -7976,10 +8092,10 @@
         <v>22.7810374063815</v>
       </c>
       <c r="U7" s="2" t="n">
-        <v>81.43857103579776</v>
+        <v>69.8307226009985</v>
       </c>
       <c r="V7" s="2" t="n">
-        <v>59.6082356678519</v>
+        <v>59.77915649033152</v>
       </c>
     </row>
     <row r="8">
@@ -8046,10 +8162,10 @@
         <v>2.017588459932436</v>
       </c>
       <c r="U8" s="2" t="n">
-        <v>2.983492934349642</v>
+        <v>3.13336965565452</v>
       </c>
       <c r="V8" s="2" t="n">
-        <v>4.12098512225864</v>
+        <v>4.076903184343629</v>
       </c>
     </row>
     <row r="9">
@@ -8116,10 +8232,10 @@
         <v>10.87213705956044</v>
       </c>
       <c r="U9" s="2" t="n">
-        <v>20.37665927427547</v>
+        <v>21.3717736299582</v>
       </c>
       <c r="V9" s="2" t="n">
-        <v>34.77571014872512</v>
+        <v>35.71211791968918</v>
       </c>
     </row>
     <row r="10">
@@ -8186,10 +8302,10 @@
         <v>25.48900096933077</v>
       </c>
       <c r="U10" s="2" t="n">
-        <v>115.4182934698164</v>
+        <v>106.2196904182567</v>
       </c>
       <c r="V10" s="2" t="n">
-        <v>15241.14851623251</v>
+        <v>14877.93741284232</v>
       </c>
     </row>
     <row r="11">
@@ -8256,10 +8372,10 @@
         <v>37.01493907846017</v>
       </c>
       <c r="U11" s="2" t="n">
-        <v>170.6887237543336</v>
+        <v>147.5812828659979</v>
       </c>
       <c r="V11" s="2" t="n">
-        <v>257.6673176573593</v>
+        <v>273.2189846219271</v>
       </c>
     </row>
     <row r="12">
@@ -8326,10 +8442,10 @@
         <v>44.38971537530528</v>
       </c>
       <c r="U12" s="2" t="n">
-        <v>155.2398939433816</v>
+        <v>155.5269499733022</v>
       </c>
       <c r="V12" s="2" t="n">
-        <v>187.5776355700277</v>
+        <v>203.4330067474349</v>
       </c>
     </row>
     <row r="13">
@@ -8396,10 +8512,10 @@
         <v>142.1843919903361</v>
       </c>
       <c r="U13" s="2" t="n">
-        <v>619.2551609800333</v>
+        <v>550.6230027330051</v>
       </c>
       <c r="V13" s="2" t="n">
-        <v>453.0361372714805</v>
+        <v>471.8097034434562</v>
       </c>
     </row>
     <row r="14">
@@ -8466,10 +8582,10 @@
         <v>75.9453993065396</v>
       </c>
       <c r="U14" s="2" t="n">
-        <v>320.822432898238</v>
+        <v>288.5903086732923</v>
       </c>
       <c r="V14" s="2" t="n">
-        <v>1821.949146666326</v>
+        <v>1722.34384103534</v>
       </c>
     </row>
     <row r="15">
@@ -8536,10 +8652,10 @@
         <v>23.98142182176431</v>
       </c>
       <c r="U15" s="2" t="n">
-        <v>77.57888239456308</v>
+        <v>68.98158964326262</v>
       </c>
       <c r="V15" s="2" t="n">
-        <v>123.2087982286978</v>
+        <v>121.8463895038143</v>
       </c>
     </row>
     <row r="16">
@@ -8606,10 +8722,10 @@
         <v>17.40210571612738</v>
       </c>
       <c r="U16" s="2" t="n">
-        <v>36.10829061840167</v>
+        <v>36.80762559128662</v>
       </c>
       <c r="V16" s="2" t="n">
-        <v>93.50725180020996</v>
+        <v>94.42462805535909</v>
       </c>
     </row>
     <row r="17">
@@ -8676,10 +8792,10 @@
         <v>441.4514780752895</v>
       </c>
       <c r="U17" s="2" t="n">
-        <v>4543.691069600135</v>
+        <v>3363.787374222307</v>
       </c>
       <c r="V17" s="2" t="n">
-        <v>5107.845289991419</v>
+        <v>6233.035289922082</v>
       </c>
     </row>
     <row r="18">
@@ -8746,10 +8862,10 @@
         <v>2098.815049380803</v>
       </c>
       <c r="U18" s="2" t="n">
-        <v>77538.51278903786</v>
+        <v>125580.9580385296</v>
       </c>
       <c r="V18" s="2" t="n">
-        <v>376102.081527669</v>
+        <v>1095224.597367184</v>
       </c>
     </row>
     <row r="19">
@@ -8816,10 +8932,10 @@
         <v>181.1546416749435</v>
       </c>
       <c r="U19" s="2" t="n">
-        <v>2141.070009355116</v>
+        <v>1563.239343021115</v>
       </c>
       <c r="V19" s="2" t="n">
-        <v>2413.536958955666</v>
+        <v>2786.139764177064</v>
       </c>
     </row>
     <row r="20">
@@ -8886,10 +9002,10 @@
         <v>1835.974420509146</v>
       </c>
       <c r="U20" s="2" t="n">
-        <v>45014.36440658045</v>
+        <v>68000.60919240557</v>
       </c>
       <c r="V20" s="2" t="n">
-        <v>553523.0843808699</v>
+        <v>1645094.341484428</v>
       </c>
     </row>
     <row r="21">
@@ -8956,10 +9072,10 @@
         <v>10.35309527955403</v>
       </c>
       <c r="U21" s="2" t="n">
-        <v>22.31424320996268</v>
+        <v>20.67031609222641</v>
       </c>
       <c r="V21" s="2" t="n">
-        <v>23.08419125913939</v>
+        <v>23.7201163809729</v>
       </c>
     </row>
     <row r="22">
@@ -9026,10 +9142,10 @@
         <v>82.5145022198011</v>
       </c>
       <c r="U22" s="2" t="n">
-        <v>337.6323632192312</v>
+        <v>299.6056369087224</v>
       </c>
       <c r="V22" s="2" t="n">
-        <v>299.6173327395348</v>
+        <v>310.1782655945706</v>
       </c>
     </row>
     <row r="23">
@@ -9096,10 +9212,10 @@
         <v>24.5480268157923</v>
       </c>
       <c r="U23" s="2" t="n">
-        <v>105.8865341817734</v>
+        <v>98.75863916971537</v>
       </c>
       <c r="V23" s="2" t="n">
-        <v>808.0683034516113</v>
+        <v>768.3150282244065</v>
       </c>
     </row>
     <row r="24">
@@ -9166,10 +9282,10 @@
         <v>184.0673282958193</v>
       </c>
       <c r="U24" s="2" t="n">
-        <v>795.9394278252513</v>
+        <v>701.5793292129669</v>
       </c>
       <c r="V24" s="2" t="n">
-        <v>707.689575465899</v>
+        <v>748.5026573846656</v>
       </c>
     </row>
     <row r="25">
@@ -9236,10 +9352,10 @@
         <v>438.8976480164774</v>
       </c>
       <c r="U25" s="2" t="n">
-        <v>2045.106697564957</v>
+        <v>1890.2154688351</v>
       </c>
       <c r="V25" s="2" t="n">
-        <v>2865.160909975357</v>
+        <v>2766.021116765205</v>
       </c>
     </row>
     <row r="26">
@@ -9306,10 +9422,10 @@
         <v>356.6715646359351</v>
       </c>
       <c r="U26" s="2" t="n">
-        <v>1753.2113843777</v>
+        <v>1571.516221606758</v>
       </c>
       <c r="V26" s="2" t="n">
-        <v>2483.004557003551</v>
+        <v>2351.352010120519</v>
       </c>
     </row>
     <row r="27">
@@ -9376,7 +9492,7 @@
         <v>64351.12625726748</v>
       </c>
       <c r="U27" s="2" t="n">
-        <v>380326.7529397003</v>
+        <v>337644.5780228017</v>
       </c>
       <c r="V27" s="2" t="n">
         <v>0</v>
@@ -9446,10 +9562,10 @@
         <v>38693.42214073123</v>
       </c>
       <c r="U28" s="2" t="n">
-        <v>372197.7840953156</v>
+        <v>444402.7360572153</v>
       </c>
       <c r="V28" s="2" t="n">
-        <v>4663973.032452663</v>
+        <v>12867258.24483938</v>
       </c>
     </row>
     <row r="29">
@@ -9516,7 +9632,7 @@
         <v>12359.60479087096</v>
       </c>
       <c r="U29" s="2" t="n">
-        <v>98244.16132433986</v>
+        <v>80536.99363237218</v>
       </c>
       <c r="V29" s="2" t="n">
         <v>0</v>
@@ -9586,10 +9702,10 @@
         <v>271730.3462542624</v>
       </c>
       <c r="U30" s="2" t="n">
-        <v>3785171.073549521</v>
+        <v>3850028.862905373</v>
       </c>
       <c r="V30" s="2" t="n">
-        <v>425797580.7539435</v>
+        <v>1414639309.654173</v>
       </c>
     </row>
     <row r="31">
@@ -9656,10 +9772,10 @@
         <v>24175.56556988574</v>
       </c>
       <c r="U31" s="2" t="n">
-        <v>140024.3572726357</v>
+        <v>128841.0239714557</v>
       </c>
       <c r="V31" s="2" t="n">
-        <v>493327.6906105255</v>
+        <v>484185.117512574</v>
       </c>
     </row>
   </sheetData>
@@ -11225,25 +11341,25 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>75</v>
+        <v>100</v>
       </c>
       <c r="C2" t="n">
-        <v>72</v>
+        <v>91</v>
       </c>
       <c r="D2" t="n">
         <v>0</v>
       </c>
       <c r="E2" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>0.04</v>
+        <v>0.09</v>
       </c>
       <c r="G2" s="2" t="n">
         <v>0</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>0.04</v>
+        <v>0.09</v>
       </c>
     </row>
     <row r="3">
@@ -11253,25 +11369,25 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>75</v>
+        <v>100</v>
       </c>
       <c r="C3" t="n">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="D3" t="n">
         <v>0</v>
       </c>
       <c r="E3" t="n">
-        <v>66</v>
+        <v>83</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>0.88</v>
+        <v>0.83</v>
       </c>
       <c r="G3" s="2" t="n">
         <v>0</v>
       </c>
       <c r="H3" s="2" t="n">
-        <v>0.88</v>
+        <v>0.83</v>
       </c>
     </row>
   </sheetData>
@@ -11452,7 +11568,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Christensen &amp; Pauly (1995): per-group TE^(1-TL) with global_TE=0.1.</t>
+          <t>Pauly &amp; Christensen (1995): per-group TE^(1-TL) with global_TE=0.1.</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -11469,7 +11585,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Christensen &amp; Pauly (1995): per-group TE^(1-TL) with global_TE='mean'.</t>
+          <t>Pauly &amp; Christensen (1995): per-group TE^(1-TL) with global_TE='mean'.</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">

--- a/PPREstimation/output/top10/52_1_Sea_of_Okhotsk_NE_(1980).xlsx
+++ b/PPREstimation/output/top10/52_1_Sea_of_Okhotsk_NE_(1980).xlsx
@@ -617,7 +617,6 @@
           <t>Import</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr"/>
       <c r="F2" s="2" t="n">
         <v>1</v>
       </c>
@@ -640,10 +639,10 @@
         <v>0</v>
       </c>
       <c r="M2" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="N2" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="O2" s="2" t="n">
         <v>0</v>
@@ -3245,7 +3244,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V31"/>
+  <dimension ref="A1:X31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -3383,6 +3382,16 @@
           <t>MC_new_TE_EEfix</t>
         </is>
       </c>
+      <c r="W1" t="inlineStr">
+        <is>
+          <t>SPPR_1995_TEmean_catch</t>
+        </is>
+      </c>
+      <c r="X1" t="inlineStr">
+        <is>
+          <t>Ulanowicz_globalTEmean_catch</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
@@ -3393,9 +3402,6 @@
           <t>diet_import</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr"/>
-      <c r="D2" t="inlineStr"/>
-      <c r="E2" t="inlineStr"/>
       <c r="F2" s="2" t="n">
         <v>0</v>
       </c>
@@ -3426,19 +3432,19 @@
       <c r="O2" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="P2" t="inlineStr"/>
       <c r="Q2" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="R2" t="inlineStr"/>
       <c r="S2" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="T2" t="inlineStr"/>
       <c r="U2" s="2" t="n">
         <v>0</v>
       </c>
       <c r="V2" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="X2" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3451,9 +3457,6 @@
           <t>Detritus</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr"/>
-      <c r="D3" t="inlineStr"/>
-      <c r="E3" t="inlineStr"/>
       <c r="F3" s="2" t="n">
         <v>0</v>
       </c>
@@ -3503,6 +3506,9 @@
         <v>0</v>
       </c>
       <c r="V3" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="X3" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3515,9 +3521,6 @@
           <t>Phytoplankton</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr"/>
-      <c r="D4" t="inlineStr"/>
-      <c r="E4" t="inlineStr"/>
       <c r="F4" s="2" t="n">
         <v>1</v>
       </c>
@@ -3567,6 +3570,9 @@
         <v>1</v>
       </c>
       <c r="V4" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="X4" t="n">
         <v>1</v>
       </c>
     </row>
@@ -3579,9 +3585,6 @@
           <t>Phytobenthos</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr"/>
-      <c r="D5" t="inlineStr"/>
-      <c r="E5" t="inlineStr"/>
       <c r="F5" s="2" t="n">
         <v>1</v>
       </c>
@@ -3631,6 +3634,9 @@
         <v>1</v>
       </c>
       <c r="V5" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="X5" t="n">
         <v>1</v>
       </c>
     </row>
@@ -3643,11 +3649,8 @@
           <t>Herbivorous zooplankton</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr"/>
-      <c r="D6" t="inlineStr"/>
-      <c r="E6" t="inlineStr"/>
       <c r="F6" s="2" t="n">
-        <v>2.640012522012788</v>
+        <v>2.301317548697287</v>
       </c>
       <c r="G6" s="2" t="n">
         <v>2.288910757154842</v>
@@ -3696,6 +3699,9 @@
       </c>
       <c r="V6" s="2" t="n">
         <v>2.308357824368465</v>
+      </c>
+      <c r="X6" t="n">
+        <v>2.348133226556577</v>
       </c>
     </row>
     <row r="7">
@@ -3707,11 +3713,8 @@
           <t>Predatory zooplankton</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr"/>
-      <c r="D7" t="inlineStr"/>
-      <c r="E7" t="inlineStr"/>
       <c r="F7" s="2" t="n">
-        <v>11.54176708873243</v>
+        <v>8.770279433664099</v>
       </c>
       <c r="G7" s="2" t="n">
         <v>7.951276208747637</v>
@@ -3760,6 +3763,9 @@
       </c>
       <c r="V7" s="2" t="n">
         <v>30.57866372023318</v>
+      </c>
+      <c r="X7" t="n">
+        <v>9.130736299835307</v>
       </c>
     </row>
     <row r="8">
@@ -3771,11 +3777,8 @@
           <t>2nd level benthos</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr"/>
-      <c r="D8" t="inlineStr"/>
-      <c r="E8" t="inlineStr"/>
       <c r="F8" s="2" t="n">
-        <v>1.584007513207673</v>
+        <v>1.380790529218372</v>
       </c>
       <c r="G8" s="2" t="n">
         <v>1.276188042922841</v>
@@ -3824,6 +3827,9 @@
       </c>
       <c r="V8" s="2" t="n">
         <v>1.266223979894226</v>
+      </c>
+      <c r="X8" t="n">
+        <v>1.408879935933946</v>
       </c>
     </row>
     <row r="9">
@@ -3835,11 +3841,8 @@
           <t>Carnivorous invertebrates</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr"/>
-      <c r="D9" t="inlineStr"/>
-      <c r="E9" t="inlineStr"/>
       <c r="F9" s="2" t="n">
-        <v>8.363599339661182</v>
+        <v>6.355274951930507</v>
       </c>
       <c r="G9" s="2" t="n">
         <v>10.59951914299733</v>
@@ -3888,6 +3891,9 @@
       </c>
       <c r="V9" s="2" t="n">
         <v>11.09067603768777</v>
+      </c>
+      <c r="X9" t="n">
+        <v>6.616475579590803</v>
       </c>
     </row>
     <row r="10">
@@ -3899,11 +3905,8 @@
           <t>Jellyfish</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr"/>
-      <c r="D10" t="inlineStr"/>
-      <c r="E10" t="inlineStr"/>
       <c r="F10" s="2" t="n">
-        <v>36.02567822214979</v>
+        <v>23.20128201514521</v>
       </c>
       <c r="G10" s="2" t="n">
         <v>884.2654320712849</v>
@@ -3952,6 +3955,9 @@
       </c>
       <c r="V10" s="2" t="n">
         <v>6957.067696845485</v>
+      </c>
+      <c r="X10" t="n">
+        <v>24.71678057998663</v>
       </c>
     </row>
     <row r="11">
@@ -3963,11 +3969,8 @@
           <t>Squids</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr"/>
-      <c r="D11" t="inlineStr"/>
-      <c r="E11" t="inlineStr"/>
       <c r="F11" s="2" t="n">
-        <v>59.81536868923033</v>
+        <v>39.61273764012287</v>
       </c>
       <c r="G11" s="2" t="n">
         <v>33.41168652260096</v>
@@ -4016,6 +4019,9 @@
       </c>
       <c r="V11" s="2" t="n">
         <v>139.2881081991169</v>
+      </c>
+      <c r="X11" t="n">
+        <v>42.08051921752429</v>
       </c>
     </row>
     <row r="12">
@@ -4027,11 +4033,8 @@
           <t>Crabs and shrimps</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr"/>
-      <c r="D12" t="inlineStr"/>
-      <c r="E12" t="inlineStr"/>
       <c r="F12" s="2" t="n">
-        <v>20.71216352040432</v>
+        <v>13.67204278942812</v>
       </c>
       <c r="G12" s="2" t="n">
         <v>30.29551595789478</v>
@@ -4080,6 +4083,9 @@
       </c>
       <c r="V12" s="2" t="n">
         <v>84.73603667840504</v>
+      </c>
+      <c r="X12" t="n">
+        <v>14.52095528725243</v>
       </c>
     </row>
     <row r="13">
@@ -4091,11 +4097,8 @@
           <t>Other mesopelagic fishes</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr"/>
-      <c r="D13" t="inlineStr"/>
-      <c r="E13" t="inlineStr"/>
       <c r="F13" s="2" t="n">
-        <v>56.44779934678724</v>
+        <v>37.51665593903211</v>
       </c>
       <c r="G13" s="2" t="n">
         <v>62.87784335837292</v>
@@ -4144,6 +4147,9 @@
       </c>
       <c r="V13" s="2" t="n">
         <v>241.3358580441285</v>
+      </c>
+      <c r="X13" t="n">
+        <v>39.83228908714745</v>
       </c>
     </row>
     <row r="14">
@@ -4155,11 +4161,8 @@
           <t>Bathylagidae</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr"/>
-      <c r="D14" t="inlineStr"/>
-      <c r="E14" t="inlineStr"/>
       <c r="F14" s="2" t="n">
-        <v>43.73710722116262</v>
+        <v>29.36248397311394</v>
       </c>
       <c r="G14" s="2" t="n">
         <v>279.5808728436076</v>
@@ -4208,6 +4211,9 @@
       </c>
       <c r="V14" s="2" t="n">
         <v>862.9555412761928</v>
+      </c>
+      <c r="X14" t="n">
+        <v>31.12452475130046</v>
       </c>
     </row>
     <row r="15">
@@ -4219,11 +4225,8 @@
           <t>Myctophidae</t>
         </is>
       </c>
-      <c r="C15" t="inlineStr"/>
-      <c r="D15" t="inlineStr"/>
-      <c r="E15" t="inlineStr"/>
       <c r="F15" s="2" t="n">
-        <v>21.71819258058765</v>
+        <v>15.50965073341023</v>
       </c>
       <c r="G15" s="2" t="n">
         <v>30.15162213949722</v>
@@ -4272,6 +4275,9 @@
       </c>
       <c r="V15" s="2" t="n">
         <v>61.00638723800488</v>
+      </c>
+      <c r="X15" t="n">
+        <v>16.2900525466089</v>
       </c>
     </row>
     <row r="16">
@@ -4283,11 +4289,8 @@
           <t>Ammodytidae</t>
         </is>
       </c>
-      <c r="C16" t="inlineStr"/>
-      <c r="D16" t="inlineStr"/>
-      <c r="E16" t="inlineStr"/>
       <c r="F16" s="2" t="n">
-        <v>9.616408807162506</v>
+        <v>7.118261812800782</v>
       </c>
       <c r="G16" s="2" t="n">
         <v>28.40809628866194</v>
@@ -4336,6 +4339,9 @@
       </c>
       <c r="V16" s="2" t="n">
         <v>30.16948865601263</v>
+      </c>
+      <c r="X16" t="n">
+        <v>7.438017530134218</v>
       </c>
     </row>
     <row r="17">
@@ -4347,11 +4353,8 @@
           <t>Other bottom fishes</t>
         </is>
       </c>
-      <c r="C17" t="inlineStr"/>
-      <c r="D17" t="inlineStr"/>
-      <c r="E17" t="inlineStr"/>
       <c r="F17" s="2" t="n">
-        <v>100.6275767200453</v>
+        <v>58.89036939034452</v>
       </c>
       <c r="G17" s="2" t="n">
         <v>239.4045354224563</v>
@@ -4400,6 +4403,9 @@
       </c>
       <c r="V17" s="2" t="n">
         <v>3060.457117583493</v>
+      </c>
+      <c r="X17" t="n">
+        <v>63.68512433122689</v>
       </c>
     </row>
     <row r="18">
@@ -4411,11 +4417,8 @@
           <t>Cottidae</t>
         </is>
       </c>
-      <c r="C18" t="inlineStr"/>
-      <c r="D18" t="inlineStr"/>
-      <c r="E18" t="inlineStr"/>
       <c r="F18" s="2" t="n">
-        <v>172.7316893504228</v>
+        <v>92.13356560330777</v>
       </c>
       <c r="G18" s="2" t="n">
         <v>1178.766857505088</v>
@@ -4464,6 +4467,9 @@
       </c>
       <c r="V18" s="2" t="n">
         <v>534048.733202767</v>
+      </c>
+      <c r="X18" t="n">
+        <v>100.8996397181391</v>
       </c>
     </row>
     <row r="19">
@@ -4475,11 +4481,8 @@
           <t>Pleuronectidae</t>
         </is>
       </c>
-      <c r="C19" t="inlineStr"/>
-      <c r="D19" t="inlineStr"/>
-      <c r="E19" t="inlineStr"/>
       <c r="F19" s="2" t="n">
-        <v>49.01983518812542</v>
+        <v>28.39083270025337</v>
       </c>
       <c r="G19" s="2" t="n">
         <v>132.9170707658792</v>
@@ -4528,6 +4531,9 @@
       </c>
       <c r="V19" s="2" t="n">
         <v>1351.256347786268</v>
+      </c>
+      <c r="X19" t="n">
+        <v>30.70676707937115</v>
       </c>
     </row>
     <row r="20">
@@ -4539,11 +4545,8 @@
           <t>Other Gadidae</t>
         </is>
       </c>
-      <c r="C20" t="inlineStr"/>
-      <c r="D20" t="inlineStr"/>
-      <c r="E20" t="inlineStr"/>
       <c r="F20" s="2" t="n">
-        <v>117.5248709126216</v>
+        <v>66.69950310700396</v>
       </c>
       <c r="G20" s="2" t="n">
         <v>3170.705077828824</v>
@@ -4592,6 +4595,9 @@
       </c>
       <c r="V20" s="2" t="n">
         <v>802390.1492857393</v>
+      </c>
+      <c r="X20" t="n">
+        <v>72.40288537481295</v>
       </c>
     </row>
     <row r="21">
@@ -4603,11 +4609,8 @@
           <t>Pacific Sardine</t>
         </is>
       </c>
-      <c r="C21" t="inlineStr"/>
-      <c r="D21" t="inlineStr"/>
-      <c r="E21" t="inlineStr"/>
       <c r="F21" s="2" t="n">
-        <v>7.265375408700205</v>
+        <v>5.929357810338402</v>
       </c>
       <c r="G21" s="2" t="n">
         <v>12.16148356265587</v>
@@ -4656,6 +4659,9 @@
       </c>
       <c r="V21" s="2" t="n">
         <v>16.2610545606418</v>
+      </c>
+      <c r="X21" t="n">
+        <v>6.105139364766177</v>
       </c>
     </row>
     <row r="22">
@@ -4667,11 +4673,8 @@
           <t>Capelin</t>
         </is>
       </c>
-      <c r="C22" t="inlineStr"/>
-      <c r="D22" t="inlineStr"/>
-      <c r="E22" t="inlineStr"/>
       <c r="F22" s="2" t="n">
-        <v>33.30237592639127</v>
+        <v>22.83416876340346</v>
       </c>
       <c r="G22" s="2" t="n">
         <v>51.79800239026467</v>
@@ -4720,6 +4723,9 @@
       </c>
       <c r="V22" s="2" t="n">
         <v>158.3505104971605</v>
+      </c>
+      <c r="X22" t="n">
+        <v>24.12829694442085</v>
       </c>
     </row>
     <row r="23">
@@ -4731,11 +4737,8 @@
           <t>Salmon</t>
         </is>
       </c>
-      <c r="C23" t="inlineStr"/>
-      <c r="D23" t="inlineStr"/>
-      <c r="E23" t="inlineStr"/>
       <c r="F23" s="2" t="n">
-        <v>51.91984428226138</v>
+        <v>34.2328999822808</v>
       </c>
       <c r="G23" s="2" t="n">
         <v>72.51717521560929</v>
@@ -4784,6 +4787,9 @@
       </c>
       <c r="V23" s="2" t="n">
         <v>371.5681739455553</v>
+      </c>
+      <c r="X23" t="n">
+        <v>36.37855880332653</v>
       </c>
     </row>
     <row r="24">
@@ -4795,11 +4801,8 @@
           <t>Pacific herring</t>
         </is>
       </c>
-      <c r="C24" t="inlineStr"/>
-      <c r="D24" t="inlineStr"/>
-      <c r="E24" t="inlineStr"/>
       <c r="F24" s="2" t="n">
-        <v>51.22189621877343</v>
+        <v>34.18501237167529</v>
       </c>
       <c r="G24" s="2" t="n">
         <v>102.8169274632543</v>
@@ -4848,6 +4851,9 @@
       </c>
       <c r="V24" s="2" t="n">
         <v>382.4625627660487</v>
+      </c>
+      <c r="X24" t="n">
+        <v>36.27170578623455</v>
       </c>
     </row>
     <row r="25">
@@ -4859,11 +4865,8 @@
           <t>Juv. pollock</t>
         </is>
       </c>
-      <c r="C25" t="inlineStr"/>
-      <c r="D25" t="inlineStr"/>
-      <c r="E25" t="inlineStr"/>
       <c r="F25" s="2" t="n">
-        <v>67.99412458235994</v>
+        <v>42.6336945997876</v>
       </c>
       <c r="G25" s="2" t="n">
         <v>443.3693273898904</v>
@@ -4912,6 +4915,9 @@
       </c>
       <c r="V25" s="2" t="n">
         <v>1380.632097213146</v>
+      </c>
+      <c r="X25" t="n">
+        <v>45.63004396712611</v>
       </c>
     </row>
     <row r="26">
@@ -4923,11 +4929,8 @@
           <t>Walleye pollock</t>
         </is>
       </c>
-      <c r="C26" t="inlineStr"/>
-      <c r="D26" t="inlineStr"/>
-      <c r="E26" t="inlineStr"/>
       <c r="F26" s="2" t="n">
-        <v>68.04311735299089</v>
+        <v>42.6799212343863</v>
       </c>
       <c r="G26" s="2" t="n">
         <v>389.0726358640387</v>
@@ -4976,6 +4979,9 @@
       </c>
       <c r="V26" s="2" t="n">
         <v>1186.451320717368</v>
+      </c>
+      <c r="X26" t="n">
+        <v>45.67550971275495</v>
       </c>
     </row>
     <row r="27">
@@ -4987,11 +4993,8 @@
           <t>Seabirds</t>
         </is>
       </c>
-      <c r="C27" t="inlineStr"/>
-      <c r="D27" t="inlineStr"/>
-      <c r="E27" t="inlineStr"/>
       <c r="F27" s="2" t="n">
-        <v>283.2340067207638</v>
+        <v>158.0509570120881</v>
       </c>
       <c r="G27" s="2" t="n">
         <v>0</v>
@@ -4999,7 +5002,6 @@
       <c r="H27" s="2" t="n">
         <v>279.5023086209615</v>
       </c>
-      <c r="I27" t="inlineStr"/>
       <c r="J27" s="2" t="n">
         <v>0</v>
       </c>
@@ -5038,6 +5040,9 @@
       </c>
       <c r="V27" s="2" t="n">
         <v>0</v>
+      </c>
+      <c r="X27" t="n">
+        <v>172.0770587541016</v>
       </c>
     </row>
     <row r="28">
@@ -5049,11 +5054,8 @@
           <t>Pinnipeds</t>
         </is>
       </c>
-      <c r="C28" t="inlineStr"/>
-      <c r="D28" t="inlineStr"/>
-      <c r="E28" t="inlineStr"/>
       <c r="F28" s="2" t="n">
-        <v>297.3783312139415</v>
+        <v>169.8965085776798</v>
       </c>
       <c r="G28" s="2" t="n">
         <v>92060.3101393988</v>
@@ -5102,6 +5104,9 @@
       </c>
       <c r="V28" s="2" t="n">
         <v>6283035.907771785</v>
+      </c>
+      <c r="X28" t="n">
+        <v>184.3868194370353</v>
       </c>
     </row>
     <row r="29">
@@ -5113,11 +5118,8 @@
           <t>Sperm whales</t>
         </is>
       </c>
-      <c r="C29" t="inlineStr"/>
-      <c r="D29" t="inlineStr"/>
-      <c r="E29" t="inlineStr"/>
       <c r="F29" s="2" t="n">
-        <v>313.6708876428777</v>
+        <v>179.2080128235593</v>
       </c>
       <c r="G29" s="2" t="n">
         <v>0</v>
@@ -5125,7 +5127,6 @@
       <c r="H29" s="2" t="n">
         <v>55.89107813273982</v>
       </c>
-      <c r="I29" t="inlineStr"/>
       <c r="J29" s="2" t="n">
         <v>0</v>
       </c>
@@ -5164,6 +5165,9 @@
       </c>
       <c r="V29" s="2" t="n">
         <v>0</v>
+      </c>
+      <c r="X29" t="n">
+        <v>194.5175804729221</v>
       </c>
     </row>
     <row r="30">
@@ -5175,11 +5179,8 @@
           <t>Toothed whales</t>
         </is>
       </c>
-      <c r="C30" t="inlineStr"/>
-      <c r="D30" t="inlineStr"/>
-      <c r="E30" t="inlineStr"/>
       <c r="F30" s="2" t="n">
-        <v>238.773215910952</v>
+        <v>133.0271993512209</v>
       </c>
       <c r="G30" s="2" t="n">
         <v>390249.6304845259</v>
@@ -5229,6 +5230,9 @@
       <c r="V30" s="2" t="n">
         <v>693202949.0927888</v>
       </c>
+      <c r="X30" t="n">
+        <v>144.8413364228488</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="n">
@@ -5239,11 +5243,8 @@
           <t>Baleen whales</t>
         </is>
       </c>
-      <c r="C31" t="inlineStr"/>
-      <c r="D31" t="inlineStr"/>
-      <c r="E31" t="inlineStr"/>
       <c r="F31" s="2" t="n">
-        <v>131.4271511380308</v>
+        <v>76.60972450076972</v>
       </c>
       <c r="G31" s="2" t="n">
         <v>74951.29476335137</v>
@@ -5292,6 +5293,9 @@
       </c>
       <c r="V31" s="2" t="n">
         <v>242675.1433360545</v>
+      </c>
+      <c r="X31" t="n">
+        <v>82.86840722828065</v>
       </c>
     </row>
   </sheetData>
@@ -5305,7 +5309,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V31"/>
+  <dimension ref="A1:X31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -5443,6 +5447,16 @@
           <t>MC_new_TE_EEfix</t>
         </is>
       </c>
+      <c r="W1" t="inlineStr">
+        <is>
+          <t>SPPR_1995_TEmean_catch</t>
+        </is>
+      </c>
+      <c r="X1" t="inlineStr">
+        <is>
+          <t>Ulanowicz_globalTEmean_catch</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
@@ -5492,19 +5506,22 @@
       <c r="O2" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="P2" t="inlineStr"/>
       <c r="Q2" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="R2" t="inlineStr"/>
       <c r="S2" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="T2" t="inlineStr"/>
       <c r="U2" s="2" t="n">
         <v>0</v>
       </c>
       <c r="V2" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="W2" t="n">
+        <v>1</v>
+      </c>
+      <c r="X2" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5577,6 +5594,12 @@
       <c r="V3" s="2" t="n">
         <v>0.9515593841782986</v>
       </c>
+      <c r="W3" t="n">
+        <v>1</v>
+      </c>
+      <c r="X3" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
@@ -5647,6 +5670,12 @@
       <c r="V4" s="2" t="n">
         <v>1</v>
       </c>
+      <c r="W4" t="n">
+        <v>1</v>
+      </c>
+      <c r="X4" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
@@ -5717,6 +5746,12 @@
       <c r="V5" s="2" t="n">
         <v>1</v>
       </c>
+      <c r="W5" t="n">
+        <v>1</v>
+      </c>
+      <c r="X5" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="n">
@@ -5734,10 +5769,10 @@
         <v>10</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>5.280025044025575</v>
+        <v>4.602635097394574</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>5.280025044025575</v>
+        <v>4.602635097394574</v>
       </c>
       <c r="G6" s="2" t="n">
         <v>4.577821514309684</v>
@@ -5786,6 +5821,12 @@
       </c>
       <c r="V6" s="2" t="n">
         <v>4.505329171349933</v>
+      </c>
+      <c r="W6" t="n">
+        <v>4.696266453113155</v>
+      </c>
+      <c r="X6" t="n">
+        <v>4.696266453113155</v>
       </c>
     </row>
     <row r="7">
@@ -5804,10 +5845,10 @@
         <v>99.99999999999999</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>27.87866446553728</v>
+        <v>21.18424983976836</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>23.08353417746487</v>
+        <v>17.5405588673282</v>
       </c>
       <c r="G7" s="2" t="n">
         <v>15.90255241749527</v>
@@ -5856,6 +5897,12 @@
       </c>
       <c r="V7" s="2" t="n">
         <v>59.77915649033152</v>
+      </c>
+      <c r="W7" t="n">
+        <v>22.05491859863601</v>
+      </c>
+      <c r="X7" t="n">
+        <v>18.26147259967061</v>
       </c>
     </row>
     <row r="8">
@@ -5874,10 +5921,10 @@
         <v>10</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>5.280025044025575</v>
+        <v>4.602635097394574</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>5.280025044025574</v>
+        <v>4.602635097394574</v>
       </c>
       <c r="G8" s="2" t="n">
         <v>4.253960143076137</v>
@@ -5926,6 +5973,12 @@
       </c>
       <c r="V8" s="2" t="n">
         <v>4.076903184343629</v>
+      </c>
+      <c r="W8" t="n">
+        <v>4.696266453113155</v>
+      </c>
+      <c r="X8" t="n">
+        <v>4.696266453113155</v>
       </c>
     </row>
     <row r="9">
@@ -5944,10 +5997,10 @@
         <v>99.99999999999999</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>27.87866446553728</v>
+        <v>21.18424983976836</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>27.87866446553727</v>
+        <v>21.18424983976836</v>
       </c>
       <c r="G9" s="2" t="n">
         <v>35.33173047665775</v>
@@ -5996,6 +6049,12 @@
       </c>
       <c r="V9" s="2" t="n">
         <v>35.71211791968918</v>
+      </c>
+      <c r="W9" t="n">
+        <v>22.05491859863601</v>
+      </c>
+      <c r="X9" t="n">
+        <v>22.05491859863601</v>
       </c>
     </row>
     <row r="10">
@@ -6014,10 +6073,10 @@
         <v>192.1678373016385</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>44.69612244609182</v>
+        <v>32.66594692768881</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>82.34673248644883</v>
+        <v>52.72727295358897</v>
       </c>
       <c r="G10" s="2" t="n">
         <v>2095.248025656152</v>
@@ -6066,6 +6125,12 @@
       </c>
       <c r="V10" s="2" t="n">
         <v>14877.93741284232</v>
+      </c>
+      <c r="W10" t="n">
+        <v>34.20335794997818</v>
+      </c>
+      <c r="X10" t="n">
+        <v>56.22377819574023</v>
       </c>
     </row>
     <row r="11">
@@ -6084,10 +6149,10 @@
         <v>957.3100822228713</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>142.6316473278907</v>
+        <v>94.72342790053084</v>
       </c>
       <c r="F11" s="2" t="n">
-        <v>119.6790259721415</v>
+        <v>79.26175744474504</v>
       </c>
       <c r="G11" s="2" t="n">
         <v>66.85909344832929</v>
@@ -6136,6 +6201,12 @@
       </c>
       <c r="V11" s="2" t="n">
         <v>273.2189846219271</v>
+      </c>
+      <c r="W11" t="n">
+        <v>100.5843105009133</v>
+      </c>
+      <c r="X11" t="n">
+        <v>84.19886949576215</v>
       </c>
     </row>
     <row r="12">
@@ -6154,10 +6225,10 @@
         <v>95.89664212630589</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>27.04720839963061</v>
+        <v>20.6038616514508</v>
       </c>
       <c r="F12" s="2" t="n">
-        <v>56.07159249521006</v>
+        <v>37.70118799536801</v>
       </c>
       <c r="G12" s="2" t="n">
         <v>87.69028664784985</v>
@@ -6206,6 +6277,12 @@
       </c>
       <c r="V12" s="2" t="n">
         <v>203.4330067474349</v>
+      </c>
+      <c r="W12" t="n">
+        <v>21.44281722434658</v>
+      </c>
+      <c r="X12" t="n">
+        <v>39.93433564550757</v>
       </c>
     </row>
     <row r="13">
@@ -6224,10 +6301,10 @@
         <v>803.5261221856176</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>125.6774988481667</v>
+        <v>84.34008081145512</v>
       </c>
       <c r="F13" s="2" t="n">
-        <v>112.9513560225056</v>
+        <v>75.07568037774374</v>
       </c>
       <c r="G13" s="2" t="n">
         <v>125.8278976901746</v>
@@ -6276,6 +6353,12 @@
       </c>
       <c r="V13" s="2" t="n">
         <v>471.8097034434562</v>
+      </c>
+      <c r="W13" t="n">
+        <v>89.42144416594054</v>
+      </c>
+      <c r="X13" t="n">
+        <v>79.70868801149217</v>
       </c>
     </row>
     <row r="14">
@@ -6294,10 +6377,10 @@
         <v>433.072663830632</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>80.40326471437805</v>
+        <v>55.98311339669585</v>
       </c>
       <c r="F14" s="2" t="n">
-        <v>90.8347559055665</v>
+        <v>60.95093876890394</v>
       </c>
       <c r="G14" s="2" t="n">
         <v>595.980810547916</v>
@@ -6346,6 +6429,12 @@
       </c>
       <c r="V14" s="2" t="n">
         <v>1722.34384103534</v>
+      </c>
+      <c r="W14" t="n">
+        <v>59.0359960319099</v>
+      </c>
+      <c r="X14" t="n">
+        <v>64.61365241945592</v>
       </c>
     </row>
     <row r="15">
@@ -6364,10 +6453,10 @@
         <v>148.9361077710915</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>37.17816837124528</v>
+        <v>27.58755563311879</v>
       </c>
       <c r="F15" s="2" t="n">
-        <v>44.67286555238029</v>
+        <v>31.8383297901462</v>
       </c>
       <c r="G15" s="2" t="n">
         <v>62.99526927008372</v>
@@ -6416,6 +6505,12 @@
       </c>
       <c r="V15" s="2" t="n">
         <v>121.8463895038143</v>
+      </c>
+      <c r="W15" t="n">
+        <v>28.82163947920901</v>
+      </c>
+      <c r="X15" t="n">
+        <v>33.45014159768149</v>
       </c>
     </row>
     <row r="16">
@@ -6434,10 +6529,10 @@
         <v>100.4615790278394</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>27.97159534955067</v>
+        <v>21.24902966393597</v>
       </c>
       <c r="F16" s="2" t="n">
-        <v>31.85962489709726</v>
+        <v>23.64253547366279</v>
       </c>
       <c r="G16" s="2" t="n">
         <v>94.46318860159323</v>
@@ -6486,6 +6581,12 @@
       </c>
       <c r="V16" s="2" t="n">
         <v>94.42462805535909</v>
+      </c>
+      <c r="W16" t="n">
+        <v>22.12325191669997</v>
+      </c>
+      <c r="X16" t="n">
+        <v>24.69537328805766</v>
       </c>
     </row>
     <row r="17">
@@ -6504,10 +6605,10 @@
         <v>458.5494665163353</v>
       </c>
       <c r="E17" s="2" t="n">
-        <v>83.79409714898284</v>
+        <v>58.14554747625077</v>
       </c>
       <c r="F17" s="2" t="n">
-        <v>218.4235569116157</v>
+        <v>128.9663065620963</v>
       </c>
       <c r="G17" s="2" t="n">
         <v>526.4921571234207</v>
@@ -6556,6 +6657,12 @@
       </c>
       <c r="V17" s="2" t="n">
         <v>6233.035289922082</v>
+      </c>
+      <c r="W17" t="n">
+        <v>61.34701549533092</v>
+      </c>
+      <c r="X17" t="n">
+        <v>139.2690881142819</v>
       </c>
     </row>
     <row r="18">
@@ -6574,10 +6681,10 @@
         <v>1149.569644128419</v>
       </c>
       <c r="E18" s="2" t="n">
-        <v>162.7994465457392</v>
+        <v>106.9436311896749</v>
       </c>
       <c r="F18" s="2" t="n">
-        <v>419.1319331031422</v>
+        <v>227.6776140763192</v>
       </c>
       <c r="G18" s="2" t="n">
         <v>2742.0026218271</v>
@@ -6626,6 +6733,12 @@
       </c>
       <c r="V18" s="2" t="n">
         <v>1095224.597367184</v>
+      </c>
+      <c r="W18" t="n">
+        <v>113.7425428506414</v>
+      </c>
+      <c r="X18" t="n">
+        <v>248.6773298608114</v>
       </c>
     </row>
     <row r="19">
@@ -6644,10 +6757,10 @@
         <v>233.2433400524923</v>
       </c>
       <c r="E19" s="2" t="n">
-        <v>51.41196048219524</v>
+        <v>37.14266240597716</v>
       </c>
       <c r="F19" s="2" t="n">
-        <v>126.5194176558155</v>
+        <v>75.84076780880021</v>
       </c>
       <c r="G19" s="2" t="n">
         <v>324.1174761836669</v>
@@ -6696,6 +6809,12 @@
       </c>
       <c r="V19" s="2" t="n">
         <v>2786.139764177064</v>
+      </c>
+      <c r="W19" t="n">
+        <v>38.95671499956013</v>
+      </c>
+      <c r="X19" t="n">
+        <v>81.61491907909036</v>
       </c>
     </row>
     <row r="20">
@@ -6714,10 +6833,10 @@
         <v>707.6563663686329</v>
       </c>
       <c r="E20" s="2" t="n">
-        <v>114.6526832161108</v>
+        <v>77.52663157506882</v>
       </c>
       <c r="F20" s="2" t="n">
-        <v>277.5429147385729</v>
+        <v>159.3851682131666</v>
       </c>
       <c r="G20" s="2" t="n">
         <v>7317.526805497487</v>
@@ -6766,6 +6885,12 @@
       </c>
       <c r="V20" s="2" t="n">
         <v>1645094.341484428</v>
+      </c>
+      <c r="W20" t="n">
+        <v>82.1062067044645</v>
+      </c>
+      <c r="X20" t="n">
+        <v>172.7159821560637</v>
       </c>
     </row>
     <row r="21">
@@ -6784,10 +6909,10 @@
         <v>14.25607593602188</v>
       </c>
       <c r="E21" s="2" t="n">
-        <v>6.822160362509687</v>
+        <v>5.822500744826133</v>
       </c>
       <c r="F21" s="2" t="n">
-        <v>9.974089204406337</v>
+        <v>7.886641531625287</v>
       </c>
       <c r="G21" s="2" t="n">
         <v>16.07734930921978</v>
@@ -6836,6 +6961,12 @@
       </c>
       <c r="V21" s="2" t="n">
         <v>23.7201163809729</v>
+      </c>
+      <c r="W21" t="n">
+        <v>5.959401555272611</v>
+      </c>
+      <c r="X21" t="n">
+        <v>8.157400780495703</v>
       </c>
     </row>
     <row r="22">
@@ -6854,10 +6985,10 @@
         <v>260.6153549998892</v>
       </c>
       <c r="E22" s="2" t="n">
-        <v>55.70427595599621</v>
+        <v>39.97825302781153</v>
       </c>
       <c r="F22" s="2" t="n">
-        <v>66.98390168951386</v>
+        <v>45.95644332462776</v>
       </c>
       <c r="G22" s="2" t="n">
         <v>104.2460481282354</v>
@@ -6906,6 +7037,12 @@
       </c>
       <c r="V22" s="2" t="n">
         <v>310.1782655945706</v>
+      </c>
+      <c r="W22" t="n">
+        <v>41.97151006807996</v>
+      </c>
+      <c r="X22" t="n">
+        <v>48.55654078178316</v>
       </c>
     </row>
     <row r="23">
@@ -6924,10 +7061,10 @@
         <v>537.7936739979261</v>
       </c>
       <c r="E23" s="2" t="n">
-        <v>94.02452572065314</v>
+        <v>64.62730910556859</v>
       </c>
       <c r="F23" s="2" t="n">
-        <v>104.5984655435359</v>
+        <v>68.89654834470186</v>
       </c>
       <c r="G23" s="2" t="n">
         <v>157.1760602802228</v>
@@ -6976,6 +7113,12 @@
       </c>
       <c r="V23" s="2" t="n">
         <v>768.3150282244065</v>
+      </c>
+      <c r="W23" t="n">
+        <v>68.28079088333945</v>
+      </c>
+      <c r="X23" t="n">
+        <v>73.22489200527703</v>
       </c>
     </row>
     <row r="24">
@@ -6994,10 +7137,10 @@
         <v>614.0613855691029</v>
       </c>
       <c r="E24" s="2" t="n">
-        <v>103.4813688456822</v>
+        <v>70.56716399283415</v>
       </c>
       <c r="F24" s="2" t="n">
-        <v>102.7621261364643</v>
+        <v>68.60061415059394</v>
       </c>
       <c r="G24" s="2" t="n">
         <v>206.6330656441522</v>
@@ -7046,6 +7189,12 @@
       </c>
       <c r="V24" s="2" t="n">
         <v>748.5026573846656</v>
+      </c>
+      <c r="W24" t="n">
+        <v>74.64296450565553</v>
+      </c>
+      <c r="X24" t="n">
+        <v>72.78499931797944</v>
       </c>
     </row>
     <row r="25">
@@ -7064,10 +7213,10 @@
         <v>472.1088760681196</v>
       </c>
       <c r="E25" s="2" t="n">
-        <v>85.5773999698382</v>
+        <v>59.279899273387</v>
       </c>
       <c r="F25" s="2" t="n">
-        <v>143.4905091038848</v>
+        <v>90.11143273373939</v>
       </c>
       <c r="G25" s="2" t="n">
         <v>948.2646461013878</v>
@@ -7116,6 +7265,12 @@
       </c>
       <c r="V25" s="2" t="n">
         <v>2766.021116765205</v>
+      </c>
+      <c r="W25" t="n">
+        <v>62.55976718436576</v>
+      </c>
+      <c r="X25" t="n">
+        <v>96.42460617606433</v>
       </c>
     </row>
     <row r="26">
@@ -7134,10 +7289,10 @@
         <v>443.19575516822</v>
       </c>
       <c r="E26" s="2" t="n">
-        <v>81.75704873945472</v>
+        <v>56.84734670066118</v>
       </c>
       <c r="F26" s="2" t="n">
-        <v>137.4895374643425</v>
+        <v>86.18089558214803</v>
       </c>
       <c r="G26" s="2" t="n">
         <v>811.720324648783</v>
@@ -7186,6 +7341,12 @@
       </c>
       <c r="V26" s="2" t="n">
         <v>2351.352010120519</v>
+      </c>
+      <c r="W26" t="n">
+        <v>59.95947384551975</v>
+      </c>
+      <c r="X26" t="n">
+        <v>92.23948616526582</v>
       </c>
     </row>
     <row r="27">
@@ -7204,10 +7365,10 @@
         <v>3690.679934159451</v>
       </c>
       <c r="E27" s="2" t="n">
-        <v>378.1981726321904</v>
+        <v>231.747404317973</v>
       </c>
       <c r="F27" s="2" t="n">
-        <v>592.0104834453182</v>
+        <v>330.6351772171339</v>
       </c>
       <c r="G27" s="2" t="n">
         <v>0</v>
@@ -7215,7 +7376,6 @@
       <c r="H27" s="2" t="n">
         <v>597.1070119486627</v>
       </c>
-      <c r="I27" t="inlineStr"/>
       <c r="J27" s="2" t="n">
         <v>0</v>
       </c>
@@ -7254,6 +7414,12 @@
       </c>
       <c r="V27" s="2" t="n">
         <v>0</v>
+      </c>
+      <c r="W27" t="n">
+        <v>249.0080859298023</v>
+      </c>
+      <c r="X27" t="n">
+        <v>359.9372982916983</v>
       </c>
     </row>
     <row r="28">
@@ -7272,10 +7438,10 @@
         <v>6316.900158152956</v>
       </c>
       <c r="E28" s="2" t="n">
-        <v>557.6747112644658</v>
+        <v>330.9474462171082</v>
       </c>
       <c r="F28" s="2" t="n">
-        <v>600.4669169174184</v>
+        <v>342.8897408224037</v>
       </c>
       <c r="G28" s="2" t="n">
         <v>196639.6235546877</v>
@@ -7324,6 +7490,12 @@
       </c>
       <c r="V28" s="2" t="n">
         <v>12867258.24483938</v>
+      </c>
+      <c r="W28" t="n">
+        <v>357.2719697561159</v>
+      </c>
+      <c r="X28" t="n">
+        <v>372.1577950636552</v>
       </c>
     </row>
     <row r="29">
@@ -7342,10 +7514,10 @@
         <v>8002.573841696399</v>
       </c>
       <c r="E29" s="2" t="n">
-        <v>661.6285267329362</v>
+        <v>387.1389168651923</v>
       </c>
       <c r="F29" s="2" t="n">
-        <v>636.0407247825135</v>
+        <v>363.6412451787915</v>
       </c>
       <c r="G29" s="2" t="n">
         <v>0</v>
@@ -7353,7 +7525,6 @@
       <c r="H29" s="2" t="n">
         <v>118.1627936977122</v>
       </c>
-      <c r="I29" t="inlineStr"/>
       <c r="J29" s="2" t="n">
         <v>0</v>
       </c>
@@ -7392,6 +7563,12 @@
       </c>
       <c r="V29" s="2" t="n">
         <v>0</v>
+      </c>
+      <c r="W29" t="n">
+        <v>418.7985782328224</v>
+      </c>
+      <c r="X29" t="n">
+        <v>394.6609619468547</v>
       </c>
     </row>
     <row r="30">
@@ -7410,10 +7587,10 @@
         <v>2832.954810656827</v>
       </c>
       <c r="E30" s="2" t="n">
-        <v>312.4011249072236</v>
+        <v>194.4721790061764</v>
       </c>
       <c r="F30" s="2" t="n">
-        <v>519.6938790691926</v>
+        <v>291.1028404040098</v>
       </c>
       <c r="G30" s="2" t="n">
         <v>841359.9861091692</v>
@@ -7463,6 +7640,12 @@
       <c r="V30" s="2" t="n">
         <v>1414639309.654173</v>
       </c>
+      <c r="W30" t="n">
+        <v>208.4737632540628</v>
+      </c>
+      <c r="X30" t="n">
+        <v>316.6996488939066</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="n">
@@ -7480,10 +7663,10 @@
         <v>652.8956149848666</v>
       </c>
       <c r="E31" s="2" t="n">
-        <v>108.1701370776778</v>
+        <v>73.49534453944611</v>
       </c>
       <c r="F31" s="2" t="n">
-        <v>269.9290920813721</v>
+        <v>157.3739344485984</v>
       </c>
       <c r="G31" s="2" t="n">
         <v>158437.3698017728</v>
@@ -7532,6 +7715,12 @@
       </c>
       <c r="V31" s="2" t="n">
         <v>484185.117512574</v>
+      </c>
+      <c r="W31" t="n">
+        <v>77.7819763119403</v>
+      </c>
+      <c r="X31" t="n">
+        <v>170.2280375697981</v>
       </c>
     </row>
   </sheetData>
@@ -7545,7 +7734,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V31"/>
+  <dimension ref="A1:X31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -7683,6 +7872,16 @@
           <t>MC_new_TE_EEfix</t>
         </is>
       </c>
+      <c r="W1" t="inlineStr">
+        <is>
+          <t>SPPR_1995_TEmean_catch</t>
+        </is>
+      </c>
+      <c r="X1" t="inlineStr">
+        <is>
+          <t>Ulanowicz_globalTEmean_catch</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
@@ -7732,19 +7931,22 @@
       <c r="O2" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="P2" t="inlineStr"/>
       <c r="Q2" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="R2" t="inlineStr"/>
       <c r="S2" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="T2" t="inlineStr"/>
       <c r="U2" s="2" t="n">
         <v>1</v>
       </c>
       <c r="V2" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="W2" t="n">
+        <v>1</v>
+      </c>
+      <c r="X2" t="n">
         <v>1</v>
       </c>
     </row>
@@ -7817,6 +8019,12 @@
       <c r="V3" s="2" t="n">
         <v>0.9515593841782986</v>
       </c>
+      <c r="W3" t="n">
+        <v>1</v>
+      </c>
+      <c r="X3" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
@@ -7887,6 +8095,12 @@
       <c r="V4" s="2" t="n">
         <v>1</v>
       </c>
+      <c r="W4" t="n">
+        <v>1</v>
+      </c>
+      <c r="X4" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
@@ -7957,6 +8171,12 @@
       <c r="V5" s="2" t="n">
         <v>1</v>
       </c>
+      <c r="W5" t="n">
+        <v>1</v>
+      </c>
+      <c r="X5" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="n">
@@ -7974,10 +8194,10 @@
         <v>10</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>5.280025044025575</v>
+        <v>4.602635097394574</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>5.280025044025575</v>
+        <v>4.602635097394574</v>
       </c>
       <c r="G6" s="2" t="n">
         <v>4.577821514309684</v>
@@ -8026,6 +8246,12 @@
       </c>
       <c r="V6" s="2" t="n">
         <v>4.505329171349933</v>
+      </c>
+      <c r="W6" t="n">
+        <v>4.696266453113155</v>
+      </c>
+      <c r="X6" t="n">
+        <v>4.696266453113155</v>
       </c>
     </row>
     <row r="7">
@@ -8044,10 +8270,10 @@
         <v>99.99999999999999</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>27.87866446553728</v>
+        <v>21.18424983976836</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>23.08353417746487</v>
+        <v>17.5405588673282</v>
       </c>
       <c r="G7" s="2" t="n">
         <v>15.90255241749527</v>
@@ -8096,6 +8322,12 @@
       </c>
       <c r="V7" s="2" t="n">
         <v>59.77915649033152</v>
+      </c>
+      <c r="W7" t="n">
+        <v>22.05491859863601</v>
+      </c>
+      <c r="X7" t="n">
+        <v>18.26147259967061</v>
       </c>
     </row>
     <row r="8">
@@ -8114,10 +8346,10 @@
         <v>10</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>5.280025044025575</v>
+        <v>4.602635097394574</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>5.280025044025574</v>
+        <v>4.602635097394574</v>
       </c>
       <c r="G8" s="2" t="n">
         <v>4.253960143076137</v>
@@ -8166,6 +8398,12 @@
       </c>
       <c r="V8" s="2" t="n">
         <v>4.076903184343629</v>
+      </c>
+      <c r="W8" t="n">
+        <v>4.696266453113155</v>
+      </c>
+      <c r="X8" t="n">
+        <v>4.696266453113155</v>
       </c>
     </row>
     <row r="9">
@@ -8184,10 +8422,10 @@
         <v>99.99999999999999</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>27.87866446553728</v>
+        <v>21.18424983976836</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>27.87866446553727</v>
+        <v>21.18424983976836</v>
       </c>
       <c r="G9" s="2" t="n">
         <v>35.33173047665775</v>
@@ -8236,6 +8474,12 @@
       </c>
       <c r="V9" s="2" t="n">
         <v>35.71211791968918</v>
+      </c>
+      <c r="W9" t="n">
+        <v>22.05491859863601</v>
+      </c>
+      <c r="X9" t="n">
+        <v>22.05491859863601</v>
       </c>
     </row>
     <row r="10">
@@ -8254,10 +8498,10 @@
         <v>192.1678373016385</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>44.69612244609182</v>
+        <v>32.66594692768881</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>82.34673248644883</v>
+        <v>52.72727295358897</v>
       </c>
       <c r="G10" s="2" t="n">
         <v>2095.248025656152</v>
@@ -8306,6 +8550,12 @@
       </c>
       <c r="V10" s="2" t="n">
         <v>14877.93741284232</v>
+      </c>
+      <c r="W10" t="n">
+        <v>34.20335794997818</v>
+      </c>
+      <c r="X10" t="n">
+        <v>56.22377819574023</v>
       </c>
     </row>
     <row r="11">
@@ -8324,10 +8574,10 @@
         <v>957.3100822228713</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>142.6316473278907</v>
+        <v>94.72342790053084</v>
       </c>
       <c r="F11" s="2" t="n">
-        <v>119.6790259721415</v>
+        <v>79.26175744474504</v>
       </c>
       <c r="G11" s="2" t="n">
         <v>66.85909344832929</v>
@@ -8376,6 +8626,12 @@
       </c>
       <c r="V11" s="2" t="n">
         <v>273.2189846219271</v>
+      </c>
+      <c r="W11" t="n">
+        <v>100.5843105009133</v>
+      </c>
+      <c r="X11" t="n">
+        <v>84.19886949576215</v>
       </c>
     </row>
     <row r="12">
@@ -8394,10 +8650,10 @@
         <v>95.89664212630589</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>27.04720839963061</v>
+        <v>20.6038616514508</v>
       </c>
       <c r="F12" s="2" t="n">
-        <v>56.07159249521006</v>
+        <v>37.70118799536801</v>
       </c>
       <c r="G12" s="2" t="n">
         <v>87.69028664784985</v>
@@ -8446,6 +8702,12 @@
       </c>
       <c r="V12" s="2" t="n">
         <v>203.4330067474349</v>
+      </c>
+      <c r="W12" t="n">
+        <v>21.44281722434658</v>
+      </c>
+      <c r="X12" t="n">
+        <v>39.93433564550757</v>
       </c>
     </row>
     <row r="13">
@@ -8464,10 +8726,10 @@
         <v>803.5261221856176</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>125.6774988481667</v>
+        <v>84.34008081145512</v>
       </c>
       <c r="F13" s="2" t="n">
-        <v>112.9513560225056</v>
+        <v>75.07568037774374</v>
       </c>
       <c r="G13" s="2" t="n">
         <v>125.8278976901746</v>
@@ -8516,6 +8778,12 @@
       </c>
       <c r="V13" s="2" t="n">
         <v>471.8097034434562</v>
+      </c>
+      <c r="W13" t="n">
+        <v>89.42144416594054</v>
+      </c>
+      <c r="X13" t="n">
+        <v>79.70868801149217</v>
       </c>
     </row>
     <row r="14">
@@ -8534,10 +8802,10 @@
         <v>433.072663830632</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>80.40326471437805</v>
+        <v>55.98311339669585</v>
       </c>
       <c r="F14" s="2" t="n">
-        <v>90.8347559055665</v>
+        <v>60.95093876890394</v>
       </c>
       <c r="G14" s="2" t="n">
         <v>595.980810547916</v>
@@ -8586,6 +8854,12 @@
       </c>
       <c r="V14" s="2" t="n">
         <v>1722.34384103534</v>
+      </c>
+      <c r="W14" t="n">
+        <v>59.0359960319099</v>
+      </c>
+      <c r="X14" t="n">
+        <v>64.61365241945592</v>
       </c>
     </row>
     <row r="15">
@@ -8604,10 +8878,10 @@
         <v>148.9361077710915</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>37.17816837124528</v>
+        <v>27.58755563311879</v>
       </c>
       <c r="F15" s="2" t="n">
-        <v>44.67286555238029</v>
+        <v>31.8383297901462</v>
       </c>
       <c r="G15" s="2" t="n">
         <v>62.99526927008372</v>
@@ -8656,6 +8930,12 @@
       </c>
       <c r="V15" s="2" t="n">
         <v>121.8463895038143</v>
+      </c>
+      <c r="W15" t="n">
+        <v>28.82163947920901</v>
+      </c>
+      <c r="X15" t="n">
+        <v>33.45014159768149</v>
       </c>
     </row>
     <row r="16">
@@ -8674,10 +8954,10 @@
         <v>100.4615790278394</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>27.97159534955067</v>
+        <v>21.24902966393597</v>
       </c>
       <c r="F16" s="2" t="n">
-        <v>31.85962489709726</v>
+        <v>23.64253547366279</v>
       </c>
       <c r="G16" s="2" t="n">
         <v>94.46318860159323</v>
@@ -8726,6 +9006,12 @@
       </c>
       <c r="V16" s="2" t="n">
         <v>94.42462805535909</v>
+      </c>
+      <c r="W16" t="n">
+        <v>22.12325191669997</v>
+      </c>
+      <c r="X16" t="n">
+        <v>24.69537328805766</v>
       </c>
     </row>
     <row r="17">
@@ -8744,10 +9030,10 @@
         <v>458.5494665163353</v>
       </c>
       <c r="E17" s="2" t="n">
-        <v>83.79409714898284</v>
+        <v>58.14554747625077</v>
       </c>
       <c r="F17" s="2" t="n">
-        <v>218.4235569116157</v>
+        <v>128.9663065620963</v>
       </c>
       <c r="G17" s="2" t="n">
         <v>526.4921571234207</v>
@@ -8796,6 +9082,12 @@
       </c>
       <c r="V17" s="2" t="n">
         <v>6233.035289922082</v>
+      </c>
+      <c r="W17" t="n">
+        <v>61.34701549533092</v>
+      </c>
+      <c r="X17" t="n">
+        <v>139.2690881142819</v>
       </c>
     </row>
     <row r="18">
@@ -8814,10 +9106,10 @@
         <v>1149.569644128419</v>
       </c>
       <c r="E18" s="2" t="n">
-        <v>162.7994465457392</v>
+        <v>106.9436311896749</v>
       </c>
       <c r="F18" s="2" t="n">
-        <v>419.1319331031422</v>
+        <v>227.6776140763192</v>
       </c>
       <c r="G18" s="2" t="n">
         <v>2742.0026218271</v>
@@ -8866,6 +9158,12 @@
       </c>
       <c r="V18" s="2" t="n">
         <v>1095224.597367184</v>
+      </c>
+      <c r="W18" t="n">
+        <v>113.7425428506414</v>
+      </c>
+      <c r="X18" t="n">
+        <v>248.6773298608114</v>
       </c>
     </row>
     <row r="19">
@@ -8884,10 +9182,10 @@
         <v>233.2433400524923</v>
       </c>
       <c r="E19" s="2" t="n">
-        <v>51.41196048219524</v>
+        <v>37.14266240597716</v>
       </c>
       <c r="F19" s="2" t="n">
-        <v>126.5194176558155</v>
+        <v>75.84076780880021</v>
       </c>
       <c r="G19" s="2" t="n">
         <v>324.1174761836669</v>
@@ -8936,6 +9234,12 @@
       </c>
       <c r="V19" s="2" t="n">
         <v>2786.139764177064</v>
+      </c>
+      <c r="W19" t="n">
+        <v>38.95671499956013</v>
+      </c>
+      <c r="X19" t="n">
+        <v>81.61491907909036</v>
       </c>
     </row>
     <row r="20">
@@ -8954,10 +9258,10 @@
         <v>707.6563663686329</v>
       </c>
       <c r="E20" s="2" t="n">
-        <v>114.6526832161108</v>
+        <v>77.52663157506882</v>
       </c>
       <c r="F20" s="2" t="n">
-        <v>277.5429147385729</v>
+        <v>159.3851682131666</v>
       </c>
       <c r="G20" s="2" t="n">
         <v>7317.526805497487</v>
@@ -9006,6 +9310,12 @@
       </c>
       <c r="V20" s="2" t="n">
         <v>1645094.341484428</v>
+      </c>
+      <c r="W20" t="n">
+        <v>82.1062067044645</v>
+      </c>
+      <c r="X20" t="n">
+        <v>172.7159821560637</v>
       </c>
     </row>
     <row r="21">
@@ -9024,10 +9334,10 @@
         <v>14.25607593602188</v>
       </c>
       <c r="E21" s="2" t="n">
-        <v>6.822160362509687</v>
+        <v>5.822500744826133</v>
       </c>
       <c r="F21" s="2" t="n">
-        <v>9.974089204406337</v>
+        <v>7.886641531625287</v>
       </c>
       <c r="G21" s="2" t="n">
         <v>16.07734930921978</v>
@@ -9076,6 +9386,12 @@
       </c>
       <c r="V21" s="2" t="n">
         <v>23.7201163809729</v>
+      </c>
+      <c r="W21" t="n">
+        <v>5.959401555272611</v>
+      </c>
+      <c r="X21" t="n">
+        <v>8.157400780495703</v>
       </c>
     </row>
     <row r="22">
@@ -9094,10 +9410,10 @@
         <v>260.6153549998892</v>
       </c>
       <c r="E22" s="2" t="n">
-        <v>55.70427595599621</v>
+        <v>39.97825302781153</v>
       </c>
       <c r="F22" s="2" t="n">
-        <v>66.98390168951386</v>
+        <v>45.95644332462776</v>
       </c>
       <c r="G22" s="2" t="n">
         <v>104.2460481282354</v>
@@ -9146,6 +9462,12 @@
       </c>
       <c r="V22" s="2" t="n">
         <v>310.1782655945706</v>
+      </c>
+      <c r="W22" t="n">
+        <v>41.97151006807996</v>
+      </c>
+      <c r="X22" t="n">
+        <v>48.55654078178316</v>
       </c>
     </row>
     <row r="23">
@@ -9164,10 +9486,10 @@
         <v>537.7936739979261</v>
       </c>
       <c r="E23" s="2" t="n">
-        <v>94.02452572065314</v>
+        <v>64.62730910556859</v>
       </c>
       <c r="F23" s="2" t="n">
-        <v>104.5984655435359</v>
+        <v>68.89654834470186</v>
       </c>
       <c r="G23" s="2" t="n">
         <v>157.1760602802228</v>
@@ -9216,6 +9538,12 @@
       </c>
       <c r="V23" s="2" t="n">
         <v>768.3150282244065</v>
+      </c>
+      <c r="W23" t="n">
+        <v>68.28079088333945</v>
+      </c>
+      <c r="X23" t="n">
+        <v>73.22489200527703</v>
       </c>
     </row>
     <row r="24">
@@ -9234,10 +9562,10 @@
         <v>614.0613855691029</v>
       </c>
       <c r="E24" s="2" t="n">
-        <v>103.4813688456822</v>
+        <v>70.56716399283415</v>
       </c>
       <c r="F24" s="2" t="n">
-        <v>102.7621261364643</v>
+        <v>68.60061415059394</v>
       </c>
       <c r="G24" s="2" t="n">
         <v>206.6330656441522</v>
@@ -9286,6 +9614,12 @@
       </c>
       <c r="V24" s="2" t="n">
         <v>748.5026573846656</v>
+      </c>
+      <c r="W24" t="n">
+        <v>74.64296450565553</v>
+      </c>
+      <c r="X24" t="n">
+        <v>72.78499931797944</v>
       </c>
     </row>
     <row r="25">
@@ -9304,10 +9638,10 @@
         <v>472.1088760681196</v>
       </c>
       <c r="E25" s="2" t="n">
-        <v>85.5773999698382</v>
+        <v>59.279899273387</v>
       </c>
       <c r="F25" s="2" t="n">
-        <v>143.4905091038848</v>
+        <v>90.11143273373939</v>
       </c>
       <c r="G25" s="2" t="n">
         <v>948.2646461013878</v>
@@ -9356,6 +9690,12 @@
       </c>
       <c r="V25" s="2" t="n">
         <v>2766.021116765205</v>
+      </c>
+      <c r="W25" t="n">
+        <v>62.55976718436576</v>
+      </c>
+      <c r="X25" t="n">
+        <v>96.42460617606433</v>
       </c>
     </row>
     <row r="26">
@@ -9374,10 +9714,10 @@
         <v>443.19575516822</v>
       </c>
       <c r="E26" s="2" t="n">
-        <v>81.75704873945472</v>
+        <v>56.84734670066118</v>
       </c>
       <c r="F26" s="2" t="n">
-        <v>137.4895374643425</v>
+        <v>86.18089558214803</v>
       </c>
       <c r="G26" s="2" t="n">
         <v>811.720324648783</v>
@@ -9426,6 +9766,12 @@
       </c>
       <c r="V26" s="2" t="n">
         <v>2351.352010120519</v>
+      </c>
+      <c r="W26" t="n">
+        <v>59.95947384551975</v>
+      </c>
+      <c r="X26" t="n">
+        <v>92.23948616526582</v>
       </c>
     </row>
     <row r="27">
@@ -9444,10 +9790,10 @@
         <v>3690.679934159451</v>
       </c>
       <c r="E27" s="2" t="n">
-        <v>378.1981726321904</v>
+        <v>231.747404317973</v>
       </c>
       <c r="F27" s="2" t="n">
-        <v>592.0104834453182</v>
+        <v>330.6351772171339</v>
       </c>
       <c r="G27" s="2" t="n">
         <v>0</v>
@@ -9496,6 +9842,12 @@
       </c>
       <c r="V27" s="2" t="n">
         <v>0</v>
+      </c>
+      <c r="W27" t="n">
+        <v>249.0080859298023</v>
+      </c>
+      <c r="X27" t="n">
+        <v>359.9372982916983</v>
       </c>
     </row>
     <row r="28">
@@ -9514,10 +9866,10 @@
         <v>6316.900158152956</v>
       </c>
       <c r="E28" s="2" t="n">
-        <v>557.6747112644658</v>
+        <v>330.9474462171082</v>
       </c>
       <c r="F28" s="2" t="n">
-        <v>600.4669169174184</v>
+        <v>342.8897408224037</v>
       </c>
       <c r="G28" s="2" t="n">
         <v>196639.6235546877</v>
@@ -9566,6 +9918,12 @@
       </c>
       <c r="V28" s="2" t="n">
         <v>12867258.24483938</v>
+      </c>
+      <c r="W28" t="n">
+        <v>357.2719697561159</v>
+      </c>
+      <c r="X28" t="n">
+        <v>372.1577950636552</v>
       </c>
     </row>
     <row r="29">
@@ -9584,10 +9942,10 @@
         <v>8002.573841696399</v>
       </c>
       <c r="E29" s="2" t="n">
-        <v>661.6285267329362</v>
+        <v>387.1389168651923</v>
       </c>
       <c r="F29" s="2" t="n">
-        <v>636.0407247825135</v>
+        <v>363.6412451787915</v>
       </c>
       <c r="G29" s="2" t="n">
         <v>0</v>
@@ -9636,6 +9994,12 @@
       </c>
       <c r="V29" s="2" t="n">
         <v>0</v>
+      </c>
+      <c r="W29" t="n">
+        <v>418.7985782328224</v>
+      </c>
+      <c r="X29" t="n">
+        <v>394.6609619468547</v>
       </c>
     </row>
     <row r="30">
@@ -9654,10 +10018,10 @@
         <v>2832.954810656827</v>
       </c>
       <c r="E30" s="2" t="n">
-        <v>312.4011249072236</v>
+        <v>194.4721790061764</v>
       </c>
       <c r="F30" s="2" t="n">
-        <v>519.6938790691926</v>
+        <v>291.1028404040098</v>
       </c>
       <c r="G30" s="2" t="n">
         <v>841359.9861091692</v>
@@ -9707,6 +10071,12 @@
       <c r="V30" s="2" t="n">
         <v>1414639309.654173</v>
       </c>
+      <c r="W30" t="n">
+        <v>208.4737632540628</v>
+      </c>
+      <c r="X30" t="n">
+        <v>316.6996488939066</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="n">
@@ -9724,10 +10094,10 @@
         <v>652.8956149848666</v>
       </c>
       <c r="E31" s="2" t="n">
-        <v>108.1701370776778</v>
+        <v>73.49534453944611</v>
       </c>
       <c r="F31" s="2" t="n">
-        <v>269.9290920813721</v>
+        <v>157.3739344485984</v>
       </c>
       <c r="G31" s="2" t="n">
         <v>158437.3698017728</v>
@@ -9776,6 +10146,12 @@
       </c>
       <c r="V31" s="2" t="n">
         <v>484185.117512574</v>
+      </c>
+      <c r="W31" t="n">
+        <v>77.7819763119403</v>
+      </c>
+      <c r="X31" t="n">
+        <v>170.2280375697981</v>
       </c>
     </row>
   </sheetData>
@@ -10247,7 +10623,6 @@
           <t>WARN</t>
         </is>
       </c>
-      <c r="AC2" t="inlineStr"/>
       <c r="AD2" s="2" t="n">
         <v>0.152043528728438</v>
       </c>
@@ -10373,7 +10748,6 @@
       <c r="H3" t="b">
         <v>0</v>
       </c>
-      <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr">
         <is>
           <t>Sea_of_Okhotsk_NE (1980)</t>
@@ -10437,7 +10811,6 @@
           <t>FAIL</t>
         </is>
       </c>
-      <c r="AC3" t="inlineStr"/>
       <c r="AD3" s="2" t="n">
         <v>0</v>
       </c>
@@ -10477,7 +10850,6 @@
       <c r="AP3" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="AQ3" t="inlineStr"/>
       <c r="AR3" t="n">
         <v>3</v>
       </c>
@@ -10629,7 +11001,6 @@
           <t>OK</t>
         </is>
       </c>
-      <c r="AC4" t="inlineStr"/>
       <c r="AD4" s="2" t="n">
         <v>0.137750257963045</v>
       </c>
@@ -10731,7 +11102,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G21"/>
+  <dimension ref="A1:G23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -10792,14 +11163,12 @@
       <c r="C2" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="D2" t="inlineStr"/>
       <c r="E2" s="2" t="n">
         <v>26654.1939</v>
       </c>
       <c r="F2" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="G2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
@@ -10813,14 +11182,12 @@
       <c r="C3" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="D3" t="inlineStr"/>
       <c r="E3" s="2" t="n">
         <v>26654.1939</v>
       </c>
       <c r="F3" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="G3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
@@ -10834,14 +11201,12 @@
       <c r="C4" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="D4" t="inlineStr"/>
       <c r="E4" s="2" t="n">
         <v>26654.1939</v>
       </c>
       <c r="F4" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="G4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
@@ -11265,6 +11630,50 @@
         <v>0</v>
       </c>
       <c r="G21" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>SPPR_1995_TEmean_catch</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>0</v>
+      </c>
+      <c r="C22" t="n">
+        <v>0</v>
+      </c>
+      <c r="E22" t="n">
+        <v>26654.1939</v>
+      </c>
+      <c r="F22" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Ulanowicz_globalTEmean_catch</t>
+        </is>
+      </c>
+      <c r="B23" t="n">
+        <v>0</v>
+      </c>
+      <c r="C23" t="n">
+        <v>0</v>
+      </c>
+      <c r="D23" t="n">
+        <v>0</v>
+      </c>
+      <c r="E23" t="n">
+        <v>26654.1939</v>
+      </c>
+      <c r="F23" t="n">
+        <v>0</v>
+      </c>
+      <c r="G23" t="n">
         <v>0</v>
       </c>
     </row>
@@ -11401,7 +11810,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C30"/>
+  <dimension ref="A1:C32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -11437,7 +11846,6 @@
           <t>NaN means not available, never zero. A basal source a method does not resolve is NaN, and a method that raised leaves its entire block NaN.</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
@@ -11450,7 +11858,6 @@
           <t>sppr_all, sppr_inner and sppr_PP are the same table under three source scopes, mirroring get_PPR: sppr_all sums every basal source, sppr_inner drops Import, and sppr_PP drops Import and Detritus. Each is a flat groups x methods table -- rows are group seq with the group name in the first column, one column per method, no MultiIndex. Sums are taken over each method's own basal-source columns before aggregation; the per-source breakdown itself is not written to the workbook.</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
@@ -11463,7 +11870,6 @@
           <t>SPPR_1986 and SPPR_1995 return one un-attributed SPPR column, so their value cannot be split into a PP-only part: they are NaN in sppr_PP (and in ppr_pp_only) while sppr_inner and sppr_all carry the total. A method that resolves no Detritus source (SPPR_2015) has sppr_inner equal to sppr_PP by construction.</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
@@ -11476,7 +11882,6 @@
           <t>SPPR_2015() has no only_pp_det parameter (only_pp belongs to get_PPR / get_PPR2NPP_ratio). It is called bare here and PP-only filtering is applied downstream at the get_PPR layer, which is what the ppr_pp_only column and SUM_PP already do.</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
@@ -11489,7 +11894,6 @@
           <t>Under det_open_mode='none' det_theta does not affect the recycling gain b at all (verified: identical b at theta = 1, 3 and 10). Do not read the health sheet as a theta sensitivity.</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
@@ -11502,7 +11906,6 @@
           <t>MC runs use exclude_diverged=True, so draws graded FAIL on divergence are dropped as well as draws with a negative SPPR. The two are often the same draws rather than additive -- see the mc_diagnostics sheet for the split by cause.</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
@@ -11515,7 +11918,6 @@
           <t>SPPR_EwE and the Monte-Carlo methods are called with silent=True rather than silent=False: PPRCalculator imports tqdm.notebook, whose bar needs ipywidgets and raises ImportError('IProgress not found') outside Jupyter, which makes those methods fail outright in a terminal run. Nothing is lost -- this exporter has its own progress bar, and the MC rejection counts appear in mc_diagnostics and in the run report.</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
@@ -11528,7 +11930,6 @@
           <t>diagnose_sppr grades a CONFIGURATION, not a model: a model can be healthy under one TE_option and divergent under another. Read each row with its config_ columns.</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
@@ -11541,7 +11942,6 @@
           <t>Every SPPR method, and every diagnose_sppr row, runs in a worker process with a wall-clock budget (180 s by default; --timeout SECONDS on the command line, method_timeout= from Python, and None or 0 to disable it). A method still running when the budget expires is killed and left NaN, exactly like a method that raised -- the status column of this sheet and the run report are the only places that say which of the two happened. A timeout is a statement about this machine and this model, not about the method: rerun it with a larger budget before reading anything into it.</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
@@ -11585,7 +11985,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Pauly &amp; Christensen (1995): per-group TE^(1-TL) with global_TE='mean'.</t>
+          <t>Pauly &amp; Christensen (1995): per-group TE^(1-TL) with global_TE='mean'. Arithmetic mean with consumer consumption weights.</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -11602,7 +12002,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Nullspace form of the EwE path sum, global TE at the true mean (Jensen-able on TL).</t>
+          <t>Nullspace form of the EwE path sum, global TE at the consumer consumption-weighted arithmetic mean (Jensen-able on TL).</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -11878,6 +12278,40 @@
         </is>
       </c>
       <c r="C30" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>method: SPPR_1995_TEmean_catch</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Pauly &amp; Christensen (1995): per-group TE^(1-TL) with global_TE='mean'. Arithmetic mean with consumer catch weights. Consumer biomass fallback when consumer catch is zero.</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>method: Ulanowicz_globalTEmean_catch</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Nullspace form of the EwE path sum, global TE at the consumer catch-weighted arithmetic mean. Consumer biomass fallback when consumer catch is zero (Jensen-able on TL).</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
         <is>
           <t>ok</t>
         </is>
